--- a/compare/output/dscale_Elec_downscaled_SSP434.xlsx
+++ b/compare/output/dscale_Elec_downscaled_SSP434.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3953.126633</v>
+        <v>3953.127647</v>
       </c>
       <c r="F2" t="n">
-        <v>10018.442407</v>
+        <v>10018.449326</v>
       </c>
       <c r="G2" t="n">
-        <v>18046.002082</v>
+        <v>18046.029629</v>
       </c>
       <c r="H2" t="n">
-        <v>28042.427642</v>
+        <v>28042.529181</v>
       </c>
       <c r="I2" t="n">
-        <v>38948.884687</v>
+        <v>38949.349456</v>
       </c>
       <c r="J2" t="n">
         <v>3319.583217</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>339.233963</v>
+        <v>339.234025</v>
       </c>
       <c r="F3" t="n">
-        <v>746.48591</v>
+        <v>746.4862900000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1207.907278</v>
+        <v>1207.908659</v>
       </c>
       <c r="H3" t="n">
-        <v>1752.194585</v>
+        <v>1752.199452</v>
       </c>
       <c r="I3" t="n">
-        <v>2357.272073</v>
+        <v>2357.294098</v>
       </c>
       <c r="J3" t="n">
         <v>854.44254</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>394.512477</v>
+        <v>394.512349</v>
       </c>
       <c r="F4" t="n">
-        <v>807.030835</v>
+        <v>807.0302380000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1178.451929</v>
+        <v>1178.450405</v>
       </c>
       <c r="H4" t="n">
-        <v>1585.692942</v>
+        <v>1585.689098</v>
       </c>
       <c r="I4" t="n">
-        <v>2031.432881</v>
+        <v>2031.419259</v>
       </c>
       <c r="J4" t="n">
         <v>4052.83755</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1043.989164</v>
+        <v>1043.989346</v>
       </c>
       <c r="F5" t="n">
-        <v>3118.204713</v>
+        <v>3118.20585</v>
       </c>
       <c r="G5" t="n">
-        <v>7051.756576</v>
+        <v>7051.759356</v>
       </c>
       <c r="H5" t="n">
-        <v>13088.236192</v>
+        <v>13088.236425</v>
       </c>
       <c r="I5" t="n">
-        <v>20640.324564</v>
+        <v>20640.282095</v>
       </c>
       <c r="J5" t="n">
         <v>39755.092985</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38164.008386</v>
+        <v>38164.015482</v>
       </c>
       <c r="F6" t="n">
-        <v>96317.815263</v>
+        <v>96317.860525</v>
       </c>
       <c r="G6" t="n">
-        <v>158971.480178</v>
+        <v>158971.646772</v>
       </c>
       <c r="H6" t="n">
-        <v>231076.938105</v>
+        <v>231077.530516</v>
       </c>
       <c r="I6" t="n">
-        <v>312843.584565</v>
+        <v>312846.285743</v>
       </c>
       <c r="J6" t="n">
         <v>137471.268297</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35543.087841</v>
+        <v>35543.093164</v>
       </c>
       <c r="F7" t="n">
-        <v>92581.46604699999</v>
+        <v>92581.497848</v>
       </c>
       <c r="G7" t="n">
-        <v>176684.468808</v>
+        <v>176684.571621</v>
       </c>
       <c r="H7" t="n">
-        <v>294399.554909</v>
+        <v>294399.858797</v>
       </c>
       <c r="I7" t="n">
-        <v>443055.758522</v>
+        <v>443056.845732</v>
       </c>
       <c r="J7" t="n">
         <v>588827.2813959999</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7724.059469</v>
+        <v>7724.060905</v>
       </c>
       <c r="F8" t="n">
-        <v>19899.621754</v>
+        <v>19899.631123</v>
       </c>
       <c r="G8" t="n">
-        <v>37098.606667</v>
+        <v>37098.642528</v>
       </c>
       <c r="H8" t="n">
-        <v>60339.183434</v>
+        <v>60339.314881</v>
       </c>
       <c r="I8" t="n">
-        <v>88578.489449</v>
+        <v>88579.104116</v>
       </c>
       <c r="J8" t="n">
         <v>61499.758214</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10940.015037</v>
+        <v>10940.004712</v>
       </c>
       <c r="F9" t="n">
-        <v>21606.289422</v>
+        <v>21606.23821</v>
       </c>
       <c r="G9" t="n">
-        <v>29784.2051</v>
+        <v>29784.070045</v>
       </c>
       <c r="H9" t="n">
-        <v>37257.719267</v>
+        <v>37257.379332</v>
       </c>
       <c r="I9" t="n">
-        <v>44285.599053</v>
+        <v>44284.438284</v>
       </c>
       <c r="J9" t="n">
         <v>163044.22097</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1923.715751</v>
+        <v>1923.715508</v>
       </c>
       <c r="F10" t="n">
-        <v>4363.117761</v>
+        <v>4363.116386</v>
       </c>
       <c r="G10" t="n">
-        <v>6824.401793</v>
+        <v>6824.398306</v>
       </c>
       <c r="H10" t="n">
-        <v>9762.721667</v>
+        <v>9762.71369</v>
       </c>
       <c r="I10" t="n">
-        <v>13091.695724</v>
+        <v>13091.674051</v>
       </c>
       <c r="J10" t="n">
         <v>19869.092721</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47676.757179</v>
+        <v>47676.751447</v>
       </c>
       <c r="F11" t="n">
-        <v>116048.58906</v>
+        <v>116048.539179</v>
       </c>
       <c r="G11" t="n">
-        <v>201649.112706</v>
+        <v>201648.881506</v>
       </c>
       <c r="H11" t="n">
-        <v>311132.27587</v>
+        <v>311131.351381</v>
       </c>
       <c r="I11" t="n">
-        <v>436107.705391</v>
+        <v>436103.333644</v>
       </c>
       <c r="J11" t="n">
         <v>1092011.259865</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4253.355233</v>
+        <v>4253.356288</v>
       </c>
       <c r="F12" t="n">
-        <v>10907.379221</v>
+        <v>10907.386434</v>
       </c>
       <c r="G12" t="n">
-        <v>20309.828389</v>
+        <v>20309.857744</v>
       </c>
       <c r="H12" t="n">
-        <v>33273.547422</v>
+        <v>33273.660351</v>
       </c>
       <c r="I12" t="n">
-        <v>48817.277901</v>
+        <v>48817.819664</v>
       </c>
       <c r="J12" t="n">
         <v>9706.947082000001</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13064.470867</v>
+        <v>13064.471126</v>
       </c>
       <c r="F13" t="n">
-        <v>32086.829308</v>
+        <v>32086.83029</v>
       </c>
       <c r="G13" t="n">
-        <v>55259.490794</v>
+        <v>55259.49573</v>
       </c>
       <c r="H13" t="n">
-        <v>85711.52226500001</v>
+        <v>85711.55119699999</v>
       </c>
       <c r="I13" t="n">
-        <v>123839.81649</v>
+        <v>123839.995157</v>
       </c>
       <c r="J13" t="n">
         <v>162410.276463</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>246564.018373</v>
+        <v>246563.662177</v>
       </c>
       <c r="F14" t="n">
-        <v>310531.008113</v>
+        <v>310529.832632</v>
       </c>
       <c r="G14" t="n">
-        <v>385668.580415</v>
+        <v>385665.508568</v>
       </c>
       <c r="H14" t="n">
-        <v>496118.855829</v>
+        <v>496110.650223</v>
       </c>
       <c r="I14" t="n">
-        <v>635069.9195289999</v>
+        <v>635043.127675</v>
       </c>
       <c r="J14" t="n">
         <v>889061.9577650001</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>667148.711379</v>
+        <v>667149.891085</v>
       </c>
       <c r="F15" t="n">
-        <v>927913.980203</v>
+        <v>927917.752737</v>
       </c>
       <c r="G15" t="n">
-        <v>1208859.238665</v>
+        <v>1208868.413982</v>
       </c>
       <c r="H15" t="n">
-        <v>1585420.504332</v>
+        <v>1585443.524181</v>
       </c>
       <c r="I15" t="n">
-        <v>2033640.375332</v>
+        <v>2033712.094552</v>
       </c>
       <c r="J15" t="n">
         <v>2201724.360377</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>134437.621872</v>
+        <v>134437.334863</v>
       </c>
       <c r="F16" t="n">
-        <v>149157.112981</v>
+        <v>149156.345394</v>
       </c>
       <c r="G16" t="n">
-        <v>158029.028255</v>
+        <v>158027.477892</v>
       </c>
       <c r="H16" t="n">
-        <v>179524.325708</v>
+        <v>179520.941353</v>
       </c>
       <c r="I16" t="n">
-        <v>210841.521781</v>
+        <v>210831.942311</v>
       </c>
       <c r="J16" t="n">
         <v>280595.512602</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110454.487408</v>
+        <v>110454.227308</v>
       </c>
       <c r="F17" t="n">
-        <v>138342.924357</v>
+        <v>138342.078621</v>
       </c>
       <c r="G17" t="n">
-        <v>165187.556475</v>
+        <v>165185.486766</v>
       </c>
       <c r="H17" t="n">
-        <v>201742.005314</v>
+        <v>201736.896255</v>
       </c>
       <c r="I17" t="n">
-        <v>243442.368981</v>
+        <v>243427.040813</v>
       </c>
       <c r="J17" t="n">
         <v>336248.439727</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70503.200903</v>
+        <v>70502.92450199999</v>
       </c>
       <c r="F18" t="n">
-        <v>95752.42960600001</v>
+        <v>95751.445876</v>
       </c>
       <c r="G18" t="n">
-        <v>118138.67759</v>
+        <v>118136.194192</v>
       </c>
       <c r="H18" t="n">
-        <v>148470.214117</v>
+        <v>148463.893288</v>
       </c>
       <c r="I18" t="n">
-        <v>187313.308677</v>
+        <v>187293.28895</v>
       </c>
       <c r="J18" t="n">
         <v>313892.843829</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36544.39752</v>
+        <v>36544.356841</v>
       </c>
       <c r="F19" t="n">
-        <v>61595.325384</v>
+        <v>61595.141522</v>
       </c>
       <c r="G19" t="n">
-        <v>77267.95282799999</v>
+        <v>77267.474114</v>
       </c>
       <c r="H19" t="n">
-        <v>104034.289802</v>
+        <v>104032.947615</v>
       </c>
       <c r="I19" t="n">
-        <v>135906.983498</v>
+        <v>135902.35899</v>
       </c>
       <c r="J19" t="n">
         <v>576705.483715</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10651.923647</v>
+        <v>10651.906944</v>
       </c>
       <c r="F20" t="n">
-        <v>17336.656337</v>
+        <v>17336.57673</v>
       </c>
       <c r="G20" t="n">
-        <v>21859.417038</v>
+        <v>21859.177884</v>
       </c>
       <c r="H20" t="n">
-        <v>28814.315521</v>
+        <v>28813.588598</v>
       </c>
       <c r="I20" t="n">
-        <v>35977.712904</v>
+        <v>35975.16693</v>
       </c>
       <c r="J20" t="n">
         <v>257067.583472</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>954.7272380000001</v>
+        <v>954.727177</v>
       </c>
       <c r="F21" t="n">
-        <v>1281.622856</v>
+        <v>1281.622845</v>
       </c>
       <c r="G21" t="n">
-        <v>1343.000063</v>
+        <v>1343.000325</v>
       </c>
       <c r="H21" t="n">
-        <v>1599.833561</v>
+        <v>1599.83441</v>
       </c>
       <c r="I21" t="n">
-        <v>1926.48462</v>
+        <v>1926.486727</v>
       </c>
       <c r="J21" t="n">
         <v>2280.705336</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69646.42394199999</v>
+        <v>69646.45456899999</v>
       </c>
       <c r="F22" t="n">
-        <v>118797.82809</v>
+        <v>118797.970554</v>
       </c>
       <c r="G22" t="n">
-        <v>149299.742106</v>
+        <v>149300.121272</v>
       </c>
       <c r="H22" t="n">
-        <v>199716.935362</v>
+        <v>199717.992137</v>
       </c>
       <c r="I22" t="n">
-        <v>257869.718824</v>
+        <v>257873.239004</v>
       </c>
       <c r="J22" t="n">
         <v>39110.831599</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7312.404518</v>
+        <v>7312.406633</v>
       </c>
       <c r="F23" t="n">
-        <v>13303.012826</v>
+        <v>13303.023033</v>
       </c>
       <c r="G23" t="n">
-        <v>18247.84975</v>
+        <v>18247.878325</v>
       </c>
       <c r="H23" t="n">
-        <v>27114.79169</v>
+        <v>27114.875682</v>
       </c>
       <c r="I23" t="n">
-        <v>39139.463733</v>
+        <v>39139.756273</v>
       </c>
       <c r="J23" t="n">
         <v>30845.707206</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5829.939378</v>
+        <v>5829.934591</v>
       </c>
       <c r="F24" t="n">
-        <v>9255.089515</v>
+        <v>9255.068739</v>
       </c>
       <c r="G24" t="n">
-        <v>11306.015912</v>
+        <v>11305.959721</v>
       </c>
       <c r="H24" t="n">
-        <v>14815.968407</v>
+        <v>14815.806178</v>
       </c>
       <c r="I24" t="n">
-        <v>18817.444833</v>
+        <v>18816.875029</v>
       </c>
       <c r="J24" t="n">
         <v>73170.92509400001</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1429.275773</v>
+        <v>1429.274558</v>
       </c>
       <c r="F25" t="n">
-        <v>2033.967793</v>
+        <v>2033.963605</v>
       </c>
       <c r="G25" t="n">
-        <v>2258.074008</v>
+        <v>2258.064656</v>
       </c>
       <c r="H25" t="n">
-        <v>2798.963555</v>
+        <v>2798.938985</v>
       </c>
       <c r="I25" t="n">
-        <v>3448.014992</v>
+        <v>3447.931872</v>
       </c>
       <c r="J25" t="n">
         <v>11307.941339</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24590.920257</v>
+        <v>24590.91858</v>
       </c>
       <c r="F26" t="n">
-        <v>39900.583868</v>
+        <v>39900.578944</v>
       </c>
       <c r="G26" t="n">
-        <v>47373.311015</v>
+        <v>47373.306707</v>
       </c>
       <c r="H26" t="n">
-        <v>61350.835369</v>
+        <v>61350.836527</v>
       </c>
       <c r="I26" t="n">
-        <v>78106.988557</v>
+        <v>78107.00770099999</v>
       </c>
       <c r="J26" t="n">
         <v>98390.52014399999</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>50795.271891</v>
+        <v>50795.286421</v>
       </c>
       <c r="F27" t="n">
-        <v>84587.20847899999</v>
+        <v>84587.27615999999</v>
       </c>
       <c r="G27" t="n">
-        <v>102190.299598</v>
+        <v>102190.478795</v>
       </c>
       <c r="H27" t="n">
-        <v>134334.260923</v>
+        <v>134334.76178</v>
       </c>
       <c r="I27" t="n">
-        <v>174733.082452</v>
+        <v>174734.772812</v>
       </c>
       <c r="J27" t="n">
         <v>86300.919869</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>36526.160135</v>
+        <v>36526.177985</v>
       </c>
       <c r="F28" t="n">
-        <v>54578.537549</v>
+        <v>54578.610565</v>
       </c>
       <c r="G28" t="n">
-        <v>70599.37112700001</v>
+        <v>70599.571646</v>
       </c>
       <c r="H28" t="n">
-        <v>103225.877203</v>
+        <v>103226.489481</v>
       </c>
       <c r="I28" t="n">
-        <v>149769.17418</v>
+        <v>149771.473256</v>
       </c>
       <c r="J28" t="n">
         <v>990.39482</v>
@@ -2587,49 +2587,49 @@
         <v>2045.398227</v>
       </c>
       <c r="H29" t="n">
-        <v>2846.995075</v>
+        <v>2846.995077</v>
       </c>
       <c r="I29" t="n">
-        <v>3824.977446</v>
+        <v>3824.977452</v>
       </c>
       <c r="J29" t="n">
-        <v>5131.340141</v>
+        <v>5131.340155</v>
       </c>
       <c r="K29" t="n">
-        <v>6930.387014</v>
+        <v>6930.38704</v>
       </c>
       <c r="L29" t="n">
-        <v>9250.575070999999</v>
+        <v>9250.575118999999</v>
       </c>
       <c r="M29" t="n">
-        <v>12111.737011</v>
+        <v>12111.737091</v>
       </c>
       <c r="N29" t="n">
-        <v>15862.395469</v>
+        <v>15862.395633</v>
       </c>
       <c r="O29" t="n">
-        <v>20620.627549</v>
+        <v>20620.627918</v>
       </c>
       <c r="P29" t="n">
-        <v>26399.411203</v>
+        <v>26399.412011</v>
       </c>
       <c r="Q29" t="n">
-        <v>33251.622563</v>
+        <v>33251.62421</v>
       </c>
       <c r="R29" t="n">
-        <v>41171.432702</v>
+        <v>41171.435869</v>
       </c>
       <c r="S29" t="n">
-        <v>50018.850511</v>
+        <v>50018.856459</v>
       </c>
       <c r="T29" t="n">
-        <v>59674.076757</v>
+        <v>59674.08779</v>
       </c>
       <c r="U29" t="n">
-        <v>69877.510521</v>
+        <v>69877.531317</v>
       </c>
       <c r="V29" t="n">
-        <v>80610.65138</v>
+        <v>80610.692178</v>
       </c>
     </row>
     <row r="30">
@@ -2654,58 +2654,58 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5739.405317</v>
+        <v>5739.40531</v>
       </c>
       <c r="F30" t="n">
-        <v>7044.994753</v>
+        <v>7044.994732</v>
       </c>
       <c r="G30" t="n">
-        <v>7694.536461</v>
+        <v>7694.536424</v>
       </c>
       <c r="H30" t="n">
-        <v>9519.107045000001</v>
+        <v>9519.106976999999</v>
       </c>
       <c r="I30" t="n">
-        <v>12249.244867</v>
+        <v>12249.244741</v>
       </c>
       <c r="J30" t="n">
-        <v>16530.856585</v>
+        <v>16530.856343</v>
       </c>
       <c r="K30" t="n">
-        <v>22982.507058</v>
+        <v>22982.506581</v>
       </c>
       <c r="L30" t="n">
-        <v>31852.362811</v>
+        <v>31852.361873</v>
       </c>
       <c r="M30" t="n">
-        <v>43429.69485</v>
+        <v>43429.693035</v>
       </c>
       <c r="N30" t="n">
-        <v>59231.770961</v>
+        <v>59231.767576</v>
       </c>
       <c r="O30" t="n">
-        <v>80162.19061000001</v>
+        <v>80162.184517</v>
       </c>
       <c r="P30" t="n">
-        <v>106858.549813</v>
+        <v>106858.539099</v>
       </c>
       <c r="Q30" t="n">
-        <v>140362.340223</v>
+        <v>140362.321483</v>
       </c>
       <c r="R30" t="n">
-        <v>181455.58694</v>
+        <v>181455.554083</v>
       </c>
       <c r="S30" t="n">
-        <v>230434.257344</v>
+        <v>230434.199548</v>
       </c>
       <c r="T30" t="n">
-        <v>287145.979525</v>
+        <v>287145.876994</v>
       </c>
       <c r="U30" t="n">
-        <v>351004.382251</v>
+        <v>351004.197602</v>
       </c>
       <c r="V30" t="n">
-        <v>421985.56408</v>
+        <v>421985.219885</v>
       </c>
     </row>
     <row r="31">
@@ -2730,58 +2730,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1641.416581</v>
+        <v>1641.416579</v>
       </c>
       <c r="F31" t="n">
-        <v>2397.654858</v>
+        <v>2397.654851</v>
       </c>
       <c r="G31" t="n">
-        <v>2981.462292</v>
+        <v>2981.462277</v>
       </c>
       <c r="H31" t="n">
-        <v>3912.320733</v>
+        <v>3912.320706</v>
       </c>
       <c r="I31" t="n">
-        <v>5020.849181</v>
+        <v>5020.849131</v>
       </c>
       <c r="J31" t="n">
-        <v>6498.200436</v>
+        <v>6498.200343</v>
       </c>
       <c r="K31" t="n">
-        <v>8498.601027999999</v>
+        <v>8498.600855000001</v>
       </c>
       <c r="L31" t="n">
-        <v>11010.521475</v>
+        <v>11010.521157</v>
       </c>
       <c r="M31" t="n">
-        <v>14086.447249</v>
+        <v>14086.44667</v>
       </c>
       <c r="N31" t="n">
-        <v>18208.444012</v>
+        <v>18208.442988</v>
       </c>
       <c r="O31" t="n">
-        <v>23547.073033</v>
+        <v>23547.071273</v>
       </c>
       <c r="P31" t="n">
-        <v>30123.631548</v>
+        <v>30123.62858</v>
       </c>
       <c r="Q31" t="n">
-        <v>38018.025025</v>
+        <v>38018.02004</v>
       </c>
       <c r="R31" t="n">
-        <v>47176.001963</v>
+        <v>47175.993576</v>
       </c>
       <c r="S31" t="n">
-        <v>57466.635309</v>
+        <v>57466.621151</v>
       </c>
       <c r="T31" t="n">
-        <v>68716.477101</v>
+        <v>68716.45298</v>
       </c>
       <c r="U31" t="n">
-        <v>80688.15609800001</v>
+        <v>80688.114333</v>
       </c>
       <c r="V31" t="n">
-        <v>93373.41462900001</v>
+        <v>93373.339618</v>
       </c>
     </row>
     <row r="32">
@@ -2806,58 +2806,58 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>26424.925828</v>
+        <v>26424.925795</v>
       </c>
       <c r="F32" t="n">
-        <v>35444.909248</v>
+        <v>35444.909144</v>
       </c>
       <c r="G32" t="n">
-        <v>42131.44937</v>
+        <v>42131.449168</v>
       </c>
       <c r="H32" t="n">
-        <v>53926.454519</v>
+        <v>53926.45414</v>
       </c>
       <c r="I32" t="n">
-        <v>69034.192644</v>
+        <v>69034.191951</v>
       </c>
       <c r="J32" t="n">
-        <v>90424.26485599999</v>
+        <v>90424.263565</v>
       </c>
       <c r="K32" t="n">
-        <v>120815.503216</v>
+        <v>120815.500775</v>
       </c>
       <c r="L32" t="n">
-        <v>160381.826082</v>
+        <v>160381.821478</v>
       </c>
       <c r="M32" t="n">
-        <v>210027.813517</v>
+        <v>210027.804963</v>
       </c>
       <c r="N32" t="n">
-        <v>276335.787991</v>
+        <v>276335.772616</v>
       </c>
       <c r="O32" t="n">
-        <v>362166.952268</v>
+        <v>362166.925522</v>
       </c>
       <c r="P32" t="n">
-        <v>468182.271897</v>
+        <v>468182.22639</v>
       </c>
       <c r="Q32" t="n">
-        <v>596636.406536</v>
+        <v>596636.329444</v>
       </c>
       <c r="R32" t="n">
-        <v>748262.487097</v>
+        <v>748262.356071</v>
       </c>
       <c r="S32" t="n">
-        <v>921960.074518</v>
+        <v>921959.850908</v>
       </c>
       <c r="T32" t="n">
-        <v>1116368.56063</v>
+        <v>1116368.174999</v>
       </c>
       <c r="U32" t="n">
-        <v>1328084.678613</v>
+        <v>1328084.002292</v>
       </c>
       <c r="V32" t="n">
-        <v>1557284.220883</v>
+        <v>1557282.990172</v>
       </c>
     </row>
     <row r="33">
@@ -2882,58 +2882,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>24192.260867</v>
+        <v>24192.260843</v>
       </c>
       <c r="F33" t="n">
-        <v>35348.843259</v>
+        <v>35348.843177</v>
       </c>
       <c r="G33" t="n">
-        <v>45586.444688</v>
+        <v>45586.444519</v>
       </c>
       <c r="H33" t="n">
-        <v>61288.739908</v>
+        <v>61288.739585</v>
       </c>
       <c r="I33" t="n">
-        <v>79991.368115</v>
+        <v>79991.367524</v>
       </c>
       <c r="J33" t="n">
-        <v>104251.052846</v>
+        <v>104251.051755</v>
       </c>
       <c r="K33" t="n">
-        <v>136370.754291</v>
+        <v>136370.752258</v>
       </c>
       <c r="L33" t="n">
-        <v>175919.324801</v>
+        <v>175919.321024</v>
       </c>
       <c r="M33" t="n">
-        <v>223290.32952</v>
+        <v>223290.322617</v>
       </c>
       <c r="N33" t="n">
-        <v>284871.967813</v>
+        <v>284871.955757</v>
       </c>
       <c r="O33" t="n">
-        <v>362225.376041</v>
+        <v>362225.355859</v>
       </c>
       <c r="P33" t="n">
-        <v>455049.559533</v>
+        <v>455049.526548</v>
       </c>
       <c r="Q33" t="n">
-        <v>563635.026964</v>
+        <v>563634.9732379999</v>
       </c>
       <c r="R33" t="n">
-        <v>687515.8357779999</v>
+        <v>687515.747632</v>
       </c>
       <c r="S33" t="n">
-        <v>824915.071595</v>
+        <v>824914.925936</v>
       </c>
       <c r="T33" t="n">
-        <v>973907.476727</v>
+        <v>973907.232999</v>
       </c>
       <c r="U33" t="n">
-        <v>1131242.371849</v>
+        <v>1131241.956728</v>
       </c>
       <c r="V33" t="n">
-        <v>1295459.234088</v>
+        <v>1295458.501857</v>
       </c>
     </row>
     <row r="34">
@@ -2958,58 +2958,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27165.10278</v>
+        <v>27165.102743</v>
       </c>
       <c r="F34" t="n">
-        <v>70009.591974</v>
+        <v>70009.591759</v>
       </c>
       <c r="G34" t="n">
-        <v>153038.237474</v>
+        <v>153038.236752</v>
       </c>
       <c r="H34" t="n">
-        <v>296652.99422</v>
+        <v>296652.992332</v>
       </c>
       <c r="I34" t="n">
-        <v>489800.914818</v>
+        <v>489800.910728</v>
       </c>
       <c r="J34" t="n">
-        <v>737265.451387</v>
+        <v>737265.443168</v>
       </c>
       <c r="K34" t="n">
-        <v>1052165.288717</v>
+        <v>1052165.272647</v>
       </c>
       <c r="L34" t="n">
-        <v>1428787.968336</v>
+        <v>1428787.937525</v>
       </c>
       <c r="M34" t="n">
-        <v>1872503.185561</v>
+        <v>1872503.127928</v>
       </c>
       <c r="N34" t="n">
-        <v>2441856.323378</v>
+        <v>2441856.220921</v>
       </c>
       <c r="O34" t="n">
-        <v>3160088.68764</v>
+        <v>3160088.513549</v>
       </c>
       <c r="P34" t="n">
-        <v>4029447.784831</v>
+        <v>4029447.49707</v>
       </c>
       <c r="Q34" t="n">
-        <v>5062302.752736</v>
+        <v>5062302.279231</v>
       </c>
       <c r="R34" t="n">
-        <v>6250794.93601</v>
+        <v>6250794.152968</v>
       </c>
       <c r="S34" t="n">
-        <v>7576693.843441</v>
+        <v>7576692.541347</v>
       </c>
       <c r="T34" t="n">
-        <v>9016044.734854</v>
+        <v>9016042.546409</v>
       </c>
       <c r="U34" t="n">
-        <v>10533178.601679</v>
+        <v>10533174.867395</v>
       </c>
       <c r="V34" t="n">
-        <v>12119724.382292</v>
+        <v>12119717.789233</v>
       </c>
     </row>
     <row r="35">
@@ -3034,58 +3034,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8399.795676</v>
+        <v>8399.795668999999</v>
       </c>
       <c r="F35" t="n">
-        <v>15296.408823</v>
+        <v>15296.408799</v>
       </c>
       <c r="G35" t="n">
-        <v>24086.39594</v>
+        <v>24086.395902</v>
       </c>
       <c r="H35" t="n">
-        <v>36481.762763</v>
+        <v>36481.762725</v>
       </c>
       <c r="I35" t="n">
-        <v>50174.488458</v>
+        <v>50174.48843</v>
       </c>
       <c r="J35" t="n">
-        <v>66126.103689</v>
+        <v>66126.103642</v>
       </c>
       <c r="K35" t="n">
-        <v>86021.400616</v>
+        <v>86021.400459</v>
       </c>
       <c r="L35" t="n">
-        <v>109825.739112</v>
+        <v>109825.738632</v>
       </c>
       <c r="M35" t="n">
-        <v>137948.209959</v>
+        <v>137948.208759</v>
       </c>
       <c r="N35" t="n">
-        <v>174491.05804</v>
+        <v>174491.055708</v>
       </c>
       <c r="O35" t="n">
-        <v>220059.387386</v>
+        <v>220059.383473</v>
       </c>
       <c r="P35" t="n">
-        <v>273974.214537</v>
+        <v>273974.208313</v>
       </c>
       <c r="Q35" t="n">
-        <v>335797.463891</v>
+        <v>335797.453871</v>
       </c>
       <c r="R35" t="n">
-        <v>404808.426357</v>
+        <v>404808.409581</v>
       </c>
       <c r="S35" t="n">
-        <v>479204.661897</v>
+        <v>479204.633161</v>
       </c>
       <c r="T35" t="n">
-        <v>557086.455406</v>
+        <v>557086.405291</v>
       </c>
       <c r="U35" t="n">
-        <v>635527.773145</v>
+        <v>635527.684731</v>
       </c>
       <c r="V35" t="n">
-        <v>713802.211717</v>
+        <v>713802.051245</v>
       </c>
     </row>
     <row r="36">
@@ -3110,58 +3110,58 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>174.004298</v>
+        <v>174.0043</v>
       </c>
       <c r="F36" t="n">
-        <v>258.132221</v>
+        <v>258.132229</v>
       </c>
       <c r="G36" t="n">
-        <v>298.613653</v>
+        <v>298.613668</v>
       </c>
       <c r="H36" t="n">
-        <v>346.116773</v>
+        <v>346.116797</v>
       </c>
       <c r="I36" t="n">
-        <v>389.947431</v>
+        <v>389.947467</v>
       </c>
       <c r="J36" t="n">
-        <v>449.037006</v>
+        <v>449.037061</v>
       </c>
       <c r="K36" t="n">
-        <v>528.229771</v>
+        <v>528.229857</v>
       </c>
       <c r="L36" t="n">
-        <v>619.317626</v>
+        <v>619.317761</v>
       </c>
       <c r="M36" t="n">
-        <v>713.613026</v>
+        <v>713.61323</v>
       </c>
       <c r="N36" t="n">
-        <v>822.603445</v>
+        <v>822.603755</v>
       </c>
       <c r="O36" t="n">
-        <v>945.466056</v>
+        <v>945.466524</v>
       </c>
       <c r="P36" t="n">
-        <v>1078.521228</v>
+        <v>1078.521936</v>
       </c>
       <c r="Q36" t="n">
-        <v>1220.657189</v>
+        <v>1220.658265</v>
       </c>
       <c r="R36" t="n">
-        <v>1364.77976</v>
+        <v>1364.781394</v>
       </c>
       <c r="S36" t="n">
-        <v>1501.979905</v>
+        <v>1501.98238</v>
       </c>
       <c r="T36" t="n">
-        <v>1626.955078</v>
+        <v>1626.958848</v>
       </c>
       <c r="U36" t="n">
-        <v>1736.960152</v>
+        <v>1736.966011</v>
       </c>
       <c r="V36" t="n">
-        <v>1832.683984</v>
+        <v>1832.693472</v>
       </c>
     </row>
     <row r="37">
@@ -3186,58 +3186,58 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7325.93295</v>
+        <v>7325.932981</v>
       </c>
       <c r="F37" t="n">
-        <v>9471.386842</v>
+        <v>9471.386913</v>
       </c>
       <c r="G37" t="n">
-        <v>10771.150296</v>
+        <v>10771.150411</v>
       </c>
       <c r="H37" t="n">
-        <v>13067.321831</v>
+        <v>13067.322021</v>
       </c>
       <c r="I37" t="n">
-        <v>15750.897697</v>
+        <v>15750.898003</v>
       </c>
       <c r="J37" t="n">
-        <v>19295.112416</v>
+        <v>19295.112906</v>
       </c>
       <c r="K37" t="n">
-        <v>23987.585493</v>
+        <v>23987.586273</v>
       </c>
       <c r="L37" t="n">
-        <v>29526.758264</v>
+        <v>29526.759459</v>
       </c>
       <c r="M37" t="n">
-        <v>35841.53868</v>
+        <v>35841.540463</v>
       </c>
       <c r="N37" t="n">
-        <v>43901.507911</v>
+        <v>43901.510685</v>
       </c>
       <c r="O37" t="n">
-        <v>53972.591549</v>
+        <v>53972.596059</v>
       </c>
       <c r="P37" t="n">
-        <v>65957.358255</v>
+        <v>65957.365739</v>
       </c>
       <c r="Q37" t="n">
-        <v>79771.800047</v>
+        <v>79771.812447</v>
       </c>
       <c r="R37" t="n">
-        <v>95216.83445900001</v>
+        <v>95216.854722</v>
       </c>
       <c r="S37" t="n">
-        <v>111748.473856</v>
+        <v>111748.506693</v>
       </c>
       <c r="T37" t="n">
-        <v>129066.222234</v>
+        <v>129066.275473</v>
       </c>
       <c r="U37" t="n">
-        <v>146582.143977</v>
+        <v>146582.232023</v>
       </c>
       <c r="V37" t="n">
-        <v>164308.531991</v>
+        <v>164308.683787</v>
       </c>
     </row>
     <row r="38">
@@ -3262,58 +3262,58 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>35067.40245</v>
+        <v>35067.402406</v>
       </c>
       <c r="F38" t="n">
-        <v>53593.326684</v>
+        <v>53593.326534</v>
       </c>
       <c r="G38" t="n">
-        <v>68993.754076</v>
+        <v>68993.753763</v>
       </c>
       <c r="H38" t="n">
-        <v>92821.624364</v>
+        <v>92821.62375</v>
       </c>
       <c r="I38" t="n">
-        <v>123021.627932</v>
+        <v>123021.626773</v>
       </c>
       <c r="J38" t="n">
-        <v>165811.838334</v>
+        <v>165811.836121</v>
       </c>
       <c r="K38" t="n">
-        <v>226781.443782</v>
+        <v>226781.439505</v>
       </c>
       <c r="L38" t="n">
-        <v>307051.339761</v>
+        <v>307051.331537</v>
       </c>
       <c r="M38" t="n">
-        <v>407907.32796</v>
+        <v>407907.312448</v>
       </c>
       <c r="N38" t="n">
-        <v>542293.256158</v>
+        <v>542293.228017</v>
       </c>
       <c r="O38" t="n">
-        <v>716961.278356</v>
+        <v>716961.229132</v>
       </c>
       <c r="P38" t="n">
-        <v>936165.971502</v>
+        <v>936165.887292</v>
       </c>
       <c r="Q38" t="n">
-        <v>1207204.219247</v>
+        <v>1207204.075703</v>
       </c>
       <c r="R38" t="n">
-        <v>1534976.697837</v>
+        <v>1534976.452006</v>
       </c>
       <c r="S38" t="n">
-        <v>1918920.44832</v>
+        <v>1918920.025544</v>
       </c>
       <c r="T38" t="n">
-        <v>2354196.025134</v>
+        <v>2354195.29149</v>
       </c>
       <c r="U38" t="n">
-        <v>2830908.299052</v>
+        <v>2830907.007629</v>
       </c>
       <c r="V38" t="n">
-        <v>3345408.538839</v>
+        <v>3345406.187011</v>
       </c>
     </row>
     <row r="39">
@@ -3338,58 +3338,58 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3728.77454</v>
+        <v>3728.774535</v>
       </c>
       <c r="F39" t="n">
-        <v>5018.049276</v>
+        <v>5018.049262</v>
       </c>
       <c r="G39" t="n">
-        <v>6081.88985</v>
+        <v>6081.889822</v>
       </c>
       <c r="H39" t="n">
-        <v>7894.197109</v>
+        <v>7894.197055</v>
       </c>
       <c r="I39" t="n">
-        <v>10136.807064</v>
+        <v>10136.806965</v>
       </c>
       <c r="J39" t="n">
-        <v>13154.117288</v>
+        <v>13154.117106</v>
       </c>
       <c r="K39" t="n">
-        <v>17198.545117</v>
+        <v>17198.544779</v>
       </c>
       <c r="L39" t="n">
-        <v>22168.097749</v>
+        <v>22168.097128</v>
       </c>
       <c r="M39" t="n">
-        <v>28023.223706</v>
+        <v>28023.222589</v>
       </c>
       <c r="N39" t="n">
-        <v>35512.309523</v>
+        <v>35512.307583</v>
       </c>
       <c r="O39" t="n">
-        <v>44922.640616</v>
+        <v>44922.637348</v>
       </c>
       <c r="P39" t="n">
-        <v>56391.42274</v>
+        <v>56391.417328</v>
       </c>
       <c r="Q39" t="n">
-        <v>70249.215688</v>
+        <v>70249.20670900001</v>
       </c>
       <c r="R39" t="n">
-        <v>86623.580368</v>
+        <v>86623.565346</v>
       </c>
       <c r="S39" t="n">
-        <v>105395.463323</v>
+        <v>105395.437992</v>
       </c>
       <c r="T39" t="n">
-        <v>126285.767387</v>
+        <v>126285.724139</v>
       </c>
       <c r="U39" t="n">
-        <v>148867.053582</v>
+        <v>148866.978394</v>
       </c>
       <c r="V39" t="n">
-        <v>173163.504571</v>
+        <v>173163.368756</v>
       </c>
     </row>
     <row r="40">
@@ -3414,58 +3414,58 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>568.32355</v>
+        <v>568.323549</v>
       </c>
       <c r="F40" t="n">
-        <v>838.2676279999999</v>
+        <v>838.267626</v>
       </c>
       <c r="G40" t="n">
-        <v>1071.007975</v>
+        <v>1071.007971</v>
       </c>
       <c r="H40" t="n">
-        <v>1402.435863</v>
+        <v>1402.435854</v>
       </c>
       <c r="I40" t="n">
-        <v>1793.154637</v>
+        <v>1793.154622</v>
       </c>
       <c r="J40" t="n">
-        <v>2290.002029</v>
+        <v>2290.002001</v>
       </c>
       <c r="K40" t="n">
-        <v>2960.480052</v>
+        <v>2960.480001</v>
       </c>
       <c r="L40" t="n">
-        <v>3795.199592</v>
+        <v>3795.199499</v>
       </c>
       <c r="M40" t="n">
-        <v>4816.963261</v>
+        <v>4816.963091</v>
       </c>
       <c r="N40" t="n">
-        <v>6156.908558</v>
+        <v>6156.908262</v>
       </c>
       <c r="O40" t="n">
-        <v>7863.332405</v>
+        <v>7863.331907</v>
       </c>
       <c r="P40" t="n">
-        <v>9928.249035000001</v>
+        <v>9928.248217</v>
       </c>
       <c r="Q40" t="n">
-        <v>12384.133024</v>
+        <v>12384.131681</v>
       </c>
       <c r="R40" t="n">
-        <v>15218.690287</v>
+        <v>15218.688073</v>
       </c>
       <c r="S40" t="n">
-        <v>18384.962124</v>
+        <v>18384.958458</v>
       </c>
       <c r="T40" t="n">
-        <v>21845.550307</v>
+        <v>21845.544163</v>
       </c>
       <c r="U40" t="n">
-        <v>25500.690512</v>
+        <v>25500.680057</v>
       </c>
       <c r="V40" t="n">
-        <v>29371.484742</v>
+        <v>29371.466279</v>
       </c>
     </row>
     <row r="41">
@@ -3496,52 +3496,52 @@
         <v>1103.506093</v>
       </c>
       <c r="G41" t="n">
-        <v>1469.568961</v>
+        <v>1469.568963</v>
       </c>
       <c r="H41" t="n">
-        <v>1978.482812</v>
+        <v>1978.482816</v>
       </c>
       <c r="I41" t="n">
-        <v>2559.65081</v>
+        <v>2559.650817</v>
       </c>
       <c r="J41" t="n">
-        <v>3306.501545</v>
+        <v>3306.501558</v>
       </c>
       <c r="K41" t="n">
-        <v>4290.137837</v>
+        <v>4290.137856</v>
       </c>
       <c r="L41" t="n">
-        <v>5484.037493</v>
+        <v>5484.037517</v>
       </c>
       <c r="M41" t="n">
-        <v>6895.772448</v>
+        <v>6895.772471</v>
       </c>
       <c r="N41" t="n">
-        <v>8712.309703999999</v>
+        <v>8712.309732</v>
       </c>
       <c r="O41" t="n">
-        <v>10971.006106</v>
+        <v>10971.006157</v>
       </c>
       <c r="P41" t="n">
-        <v>13658.50925</v>
+        <v>13658.509356</v>
       </c>
       <c r="Q41" t="n">
-        <v>16796.156772</v>
+        <v>16796.156975</v>
       </c>
       <c r="R41" t="n">
-        <v>20369.737711</v>
+        <v>20369.738058</v>
       </c>
       <c r="S41" t="n">
-        <v>24321.990841</v>
+        <v>24321.9914</v>
       </c>
       <c r="T41" t="n">
-        <v>28578.160318</v>
+        <v>28578.161188</v>
       </c>
       <c r="U41" t="n">
-        <v>33021.711558</v>
+        <v>33021.712928</v>
       </c>
       <c r="V41" t="n">
-        <v>37596.392044</v>
+        <v>37596.394341</v>
       </c>
     </row>
     <row r="42">
@@ -3566,58 +3566,58 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3940.535335</v>
+        <v>3940.535492</v>
       </c>
       <c r="F42" t="n">
-        <v>5630.92379</v>
+        <v>5630.924255</v>
       </c>
       <c r="G42" t="n">
-        <v>7039.960967</v>
+        <v>7039.961894</v>
       </c>
       <c r="H42" t="n">
-        <v>9142.495532000001</v>
+        <v>9142.497267999999</v>
       </c>
       <c r="I42" t="n">
-        <v>11564.980397</v>
+        <v>11564.983449</v>
       </c>
       <c r="J42" t="n">
-        <v>14744.845498</v>
+        <v>14744.850787</v>
       </c>
       <c r="K42" t="n">
-        <v>18867.236723</v>
+        <v>18867.245698</v>
       </c>
       <c r="L42" t="n">
-        <v>23845.198285</v>
+        <v>23845.213096</v>
       </c>
       <c r="M42" t="n">
-        <v>29414.11627</v>
+        <v>29414.139783</v>
       </c>
       <c r="N42" t="n">
-        <v>36286.734275</v>
+        <v>36286.771423</v>
       </c>
       <c r="O42" t="n">
-        <v>44593.67929</v>
+        <v>44593.737965</v>
       </c>
       <c r="P42" t="n">
-        <v>54091.432681</v>
+        <v>54091.524869</v>
       </c>
       <c r="Q42" t="n">
-        <v>64647.944361</v>
+        <v>64648.087544</v>
       </c>
       <c r="R42" t="n">
-        <v>75966.360544</v>
+        <v>75966.58116099999</v>
       </c>
       <c r="S42" t="n">
-        <v>87639.596403</v>
+        <v>87639.935325</v>
       </c>
       <c r="T42" t="n">
-        <v>99215.840316</v>
+        <v>99216.36367799999</v>
       </c>
       <c r="U42" t="n">
-        <v>110133.755946</v>
+        <v>110134.577149</v>
       </c>
       <c r="V42" t="n">
-        <v>120258.371095</v>
+        <v>120259.709792</v>
       </c>
     </row>
     <row r="43">
@@ -3642,58 +3642,58 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1654.590123</v>
+        <v>1654.590121</v>
       </c>
       <c r="F43" t="n">
-        <v>3292.394931</v>
+        <v>3292.394921</v>
       </c>
       <c r="G43" t="n">
-        <v>5446.345617</v>
+        <v>5446.34559</v>
       </c>
       <c r="H43" t="n">
-        <v>8853.403571000001</v>
+        <v>8853.403507999999</v>
       </c>
       <c r="I43" t="n">
-        <v>13299.271086</v>
+        <v>13299.270953</v>
       </c>
       <c r="J43" t="n">
-        <v>19344.497521</v>
+        <v>19344.497247</v>
       </c>
       <c r="K43" t="n">
-        <v>27675.868885</v>
+        <v>27675.868332</v>
       </c>
       <c r="L43" t="n">
-        <v>38515.989236</v>
+        <v>38515.988146</v>
       </c>
       <c r="M43" t="n">
-        <v>52149.190104</v>
+        <v>52149.188009</v>
       </c>
       <c r="N43" t="n">
-        <v>70339.373234</v>
+        <v>70339.36936899999</v>
       </c>
       <c r="O43" t="n">
-        <v>94001.738555</v>
+        <v>94001.731692</v>
       </c>
       <c r="P43" t="n">
-        <v>123553.597316</v>
+        <v>123553.585437</v>
       </c>
       <c r="Q43" t="n">
-        <v>159793.761179</v>
+        <v>159793.740753</v>
       </c>
       <c r="R43" t="n">
-        <v>203128.096661</v>
+        <v>203128.061494</v>
       </c>
       <c r="S43" t="n">
-        <v>253098.573198</v>
+        <v>253098.512586</v>
       </c>
       <c r="T43" t="n">
-        <v>308517.472961</v>
+        <v>308517.367901</v>
       </c>
       <c r="U43" t="n">
-        <v>367577.484399</v>
+        <v>367577.300188</v>
       </c>
       <c r="V43" t="n">
-        <v>429393.154364</v>
+        <v>429392.821</v>
       </c>
     </row>
     <row r="44">
@@ -3718,58 +3718,58 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7732.422925</v>
+        <v>7732.422916</v>
       </c>
       <c r="F44" t="n">
-        <v>12297.721953</v>
+        <v>12297.721921</v>
       </c>
       <c r="G44" t="n">
-        <v>16940.065493</v>
+        <v>16940.065424</v>
       </c>
       <c r="H44" t="n">
-        <v>24300.109697</v>
+        <v>24300.109557</v>
       </c>
       <c r="I44" t="n">
-        <v>33686.0543</v>
+        <v>33686.054029</v>
       </c>
       <c r="J44" t="n">
-        <v>46410.500434</v>
+        <v>46410.499909</v>
       </c>
       <c r="K44" t="n">
-        <v>63673.266732</v>
+        <v>63673.265713</v>
       </c>
       <c r="L44" t="n">
-        <v>85402.750174</v>
+        <v>85402.748219</v>
       </c>
       <c r="M44" t="n">
-        <v>111546.252487</v>
+        <v>111546.248823</v>
       </c>
       <c r="N44" t="n">
-        <v>145144.107486</v>
+        <v>145144.100939</v>
       </c>
       <c r="O44" t="n">
-        <v>187316.173352</v>
+        <v>187316.162141</v>
       </c>
       <c r="P44" t="n">
-        <v>238206.810665</v>
+        <v>238206.791962</v>
       </c>
       <c r="Q44" t="n">
-        <v>298872.351081</v>
+        <v>298872.319973</v>
       </c>
       <c r="R44" t="n">
-        <v>369449.931884</v>
+        <v>369449.879887</v>
       </c>
       <c r="S44" t="n">
-        <v>449098.674396</v>
+        <v>449098.587008</v>
       </c>
       <c r="T44" t="n">
-        <v>536116.199832</v>
+        <v>536116.051443</v>
       </c>
       <c r="U44" t="n">
-        <v>628012.760326</v>
+        <v>628012.504499</v>
       </c>
       <c r="V44" t="n">
-        <v>723886.967609</v>
+        <v>723886.510913</v>
       </c>
     </row>
     <row r="45">
@@ -3794,58 +3794,58 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4607.905233</v>
+        <v>4607.905228</v>
       </c>
       <c r="F45" t="n">
-        <v>7389.040475</v>
+        <v>7389.040458</v>
       </c>
       <c r="G45" t="n">
-        <v>9963.548925999999</v>
+        <v>9963.54889</v>
       </c>
       <c r="H45" t="n">
-        <v>13606.580156</v>
+        <v>13606.580087</v>
       </c>
       <c r="I45" t="n">
-        <v>17873.620475</v>
+        <v>17873.620348</v>
       </c>
       <c r="J45" t="n">
-        <v>23521.030391</v>
+        <v>23521.030154</v>
       </c>
       <c r="K45" t="n">
-        <v>31317.590835</v>
+        <v>31317.590389</v>
       </c>
       <c r="L45" t="n">
-        <v>41368.733637</v>
+        <v>41368.732795</v>
       </c>
       <c r="M45" t="n">
-        <v>54011.87914</v>
+        <v>54011.877572</v>
       </c>
       <c r="N45" t="n">
-        <v>70106.934918</v>
+        <v>70106.932143</v>
       </c>
       <c r="O45" t="n">
-        <v>90107.59368400001</v>
+        <v>90107.588993</v>
       </c>
       <c r="P45" t="n">
-        <v>114256.054607</v>
+        <v>114256.046883</v>
       </c>
       <c r="Q45" t="n">
-        <v>143743.993707</v>
+        <v>143743.981001</v>
       </c>
       <c r="R45" t="n">
-        <v>179058.625234</v>
+        <v>179058.604175</v>
       </c>
       <c r="S45" t="n">
-        <v>220132.897725</v>
+        <v>220132.86256</v>
       </c>
       <c r="T45" t="n">
-        <v>266409.728205</v>
+        <v>266409.668748</v>
       </c>
       <c r="U45" t="n">
-        <v>316796.634574</v>
+        <v>316796.532462</v>
       </c>
       <c r="V45" t="n">
-        <v>370933.429016</v>
+        <v>370933.247315</v>
       </c>
     </row>
     <row r="46">
@@ -3870,58 +3870,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1610.795046</v>
+        <v>1610.795044</v>
       </c>
       <c r="F46" t="n">
-        <v>2517.55797</v>
+        <v>2517.557963</v>
       </c>
       <c r="G46" t="n">
-        <v>3531.935604</v>
+        <v>3531.935589</v>
       </c>
       <c r="H46" t="n">
-        <v>5284.889214</v>
+        <v>5284.889182</v>
       </c>
       <c r="I46" t="n">
-        <v>8049.57213</v>
+        <v>8049.572061</v>
       </c>
       <c r="J46" t="n">
-        <v>12548.342979</v>
+        <v>12548.342832</v>
       </c>
       <c r="K46" t="n">
-        <v>19617.260728</v>
+        <v>19617.260414</v>
       </c>
       <c r="L46" t="n">
-        <v>29703.508519</v>
+        <v>29703.50786</v>
       </c>
       <c r="M46" t="n">
-        <v>43315.697152</v>
+        <v>43315.695805</v>
       </c>
       <c r="N46" t="n">
-        <v>62231.734212</v>
+        <v>62231.731616</v>
       </c>
       <c r="O46" t="n">
-        <v>87597.81838700001</v>
+        <v>87597.813649</v>
       </c>
       <c r="P46" t="n">
-        <v>120304.358933</v>
+        <v>120304.35058</v>
       </c>
       <c r="Q46" t="n">
-        <v>161410.390216</v>
+        <v>161410.375646</v>
       </c>
       <c r="R46" t="n">
-        <v>211632.033575</v>
+        <v>211632.008122</v>
       </c>
       <c r="S46" t="n">
-        <v>270877.570111</v>
+        <v>270877.525564</v>
       </c>
       <c r="T46" t="n">
-        <v>338234.428529</v>
+        <v>338234.350054</v>
       </c>
       <c r="U46" t="n">
-        <v>411940.553477</v>
+        <v>411940.413482</v>
       </c>
       <c r="V46" t="n">
-        <v>490774.332364</v>
+        <v>490774.074967</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>136559.627274</v>
+        <v>136559.627279</v>
       </c>
       <c r="F47" t="n">
-        <v>238463.373597</v>
+        <v>238463.373789</v>
       </c>
       <c r="G47" t="n">
-        <v>335122.724034</v>
+        <v>335122.724763</v>
       </c>
       <c r="H47" t="n">
-        <v>477821.512294</v>
+        <v>477821.514263</v>
       </c>
       <c r="I47" t="n">
-        <v>660592.5376170001</v>
+        <v>660592.542071</v>
       </c>
       <c r="J47" t="n">
-        <v>920836.912684</v>
+        <v>920836.922176</v>
       </c>
       <c r="K47" t="n">
-        <v>1299710.862654</v>
+        <v>1299710.882559</v>
       </c>
       <c r="L47" t="n">
-        <v>1822870.045718</v>
+        <v>1822870.086645</v>
       </c>
       <c r="M47" t="n">
-        <v>2505531.874282</v>
+        <v>2505531.95592</v>
       </c>
       <c r="N47" t="n">
-        <v>3353519.097855</v>
+        <v>3353519.249317</v>
       </c>
       <c r="O47" t="n">
-        <v>4366578.967174</v>
+        <v>4366579.232051</v>
       </c>
       <c r="P47" t="n">
-        <v>5549462.161339</v>
+        <v>5549462.609725</v>
       </c>
       <c r="Q47" t="n">
-        <v>6967472.249354</v>
+        <v>6967473.006072</v>
       </c>
       <c r="R47" t="n">
-        <v>8641287.561985999</v>
+        <v>8641288.848405</v>
       </c>
       <c r="S47" t="n">
-        <v>10564944.797685</v>
+        <v>10564946.997499</v>
       </c>
       <c r="T47" t="n">
-        <v>12689641.871999</v>
+        <v>12689645.672072</v>
       </c>
       <c r="U47" t="n">
-        <v>14943642.042257</v>
+        <v>14943648.698156</v>
       </c>
       <c r="V47" t="n">
-        <v>17282224.420947</v>
+        <v>17282236.467619</v>
       </c>
     </row>
     <row r="48">
@@ -4022,58 +4022,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12592.109684</v>
+        <v>12592.10967</v>
       </c>
       <c r="F48" t="n">
-        <v>18953.687751</v>
+        <v>18953.687704</v>
       </c>
       <c r="G48" t="n">
-        <v>24759.066113</v>
+        <v>24759.066013</v>
       </c>
       <c r="H48" t="n">
-        <v>33294.590938</v>
+        <v>33294.590742</v>
       </c>
       <c r="I48" t="n">
-        <v>43160.179872</v>
+        <v>43160.179507</v>
       </c>
       <c r="J48" t="n">
-        <v>55959.524045</v>
+        <v>55959.523364</v>
       </c>
       <c r="K48" t="n">
-        <v>73178.500738</v>
+        <v>73178.49945600001</v>
       </c>
       <c r="L48" t="n">
-        <v>95212.74909899999</v>
+        <v>95212.74669099999</v>
       </c>
       <c r="M48" t="n">
-        <v>122875.764235</v>
+        <v>122875.759768</v>
       </c>
       <c r="N48" t="n">
-        <v>160282.613943</v>
+        <v>160282.605935</v>
       </c>
       <c r="O48" t="n">
-        <v>209199.750752</v>
+        <v>209199.736856</v>
       </c>
       <c r="P48" t="n">
-        <v>270351.981576</v>
+        <v>270351.957937</v>
       </c>
       <c r="Q48" t="n">
-        <v>345118.172565</v>
+        <v>345118.132426</v>
       </c>
       <c r="R48" t="n">
-        <v>434160.935631</v>
+        <v>434160.867079</v>
       </c>
       <c r="S48" t="n">
-        <v>537293.174919</v>
+        <v>537293.057109</v>
       </c>
       <c r="T48" t="n">
-        <v>653989.5146239999</v>
+        <v>653989.309758</v>
       </c>
       <c r="U48" t="n">
-        <v>782324.854966</v>
+        <v>782324.4925319999</v>
       </c>
       <c r="V48" t="n">
-        <v>922521.815919</v>
+        <v>922521.150507</v>
       </c>
     </row>
     <row r="49">
@@ -4098,58 +4098,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2244.071819</v>
+        <v>2244.071817</v>
       </c>
       <c r="F49" t="n">
-        <v>3579.476188</v>
+        <v>3579.47618</v>
       </c>
       <c r="G49" t="n">
-        <v>4759.753683</v>
+        <v>4759.753665</v>
       </c>
       <c r="H49" t="n">
-        <v>6402.653755</v>
+        <v>6402.653721</v>
       </c>
       <c r="I49" t="n">
-        <v>8235.706076</v>
+        <v>8235.706013999999</v>
       </c>
       <c r="J49" t="n">
-        <v>10590.902742</v>
+        <v>10590.902628</v>
       </c>
       <c r="K49" t="n">
-        <v>13737.909845</v>
+        <v>13737.909631</v>
       </c>
       <c r="L49" t="n">
-        <v>17690.018693</v>
+        <v>17690.018295</v>
       </c>
       <c r="M49" t="n">
-        <v>22501.902817</v>
+        <v>22501.902086</v>
       </c>
       <c r="N49" t="n">
-        <v>28866.942321</v>
+        <v>28866.941036</v>
       </c>
       <c r="O49" t="n">
-        <v>36971.432828</v>
+        <v>36971.430653</v>
       </c>
       <c r="P49" t="n">
-        <v>46814.198092</v>
+        <v>46814.194504</v>
       </c>
       <c r="Q49" t="n">
-        <v>58455.071846</v>
+        <v>58455.065953</v>
       </c>
       <c r="R49" t="n">
-        <v>71910.853141</v>
+        <v>71910.84340699999</v>
       </c>
       <c r="S49" t="n">
-        <v>86985.152674</v>
+        <v>86985.136505</v>
       </c>
       <c r="T49" t="n">
-        <v>103426.821835</v>
+        <v>103426.794685</v>
       </c>
       <c r="U49" t="n">
-        <v>120836.528161</v>
+        <v>120836.481831</v>
       </c>
       <c r="V49" t="n">
-        <v>139107.432546</v>
+        <v>139107.350716</v>
       </c>
     </row>
     <row r="50">
@@ -4177,55 +4177,55 @@
         <v>59.919188</v>
       </c>
       <c r="F50" t="n">
-        <v>89.515181</v>
+        <v>89.515182</v>
       </c>
       <c r="G50" t="n">
-        <v>109.202766</v>
+        <v>109.202767</v>
       </c>
       <c r="H50" t="n">
         <v>135.187504</v>
       </c>
       <c r="I50" t="n">
-        <v>162.092776</v>
+        <v>162.092777</v>
       </c>
       <c r="J50" t="n">
-        <v>197.24069</v>
+        <v>197.240691</v>
       </c>
       <c r="K50" t="n">
-        <v>244.422579</v>
+        <v>244.42258</v>
       </c>
       <c r="L50" t="n">
-        <v>302.977839</v>
+        <v>302.97784</v>
       </c>
       <c r="M50" t="n">
-        <v>374.568324</v>
+        <v>374.568326</v>
       </c>
       <c r="N50" t="n">
-        <v>469.257033</v>
+        <v>469.257036</v>
       </c>
       <c r="O50" t="n">
-        <v>589.391489</v>
+        <v>589.391497</v>
       </c>
       <c r="P50" t="n">
-        <v>735.222906</v>
+        <v>735.222925</v>
       </c>
       <c r="Q50" t="n">
-        <v>910.8991130000001</v>
+        <v>910.899152</v>
       </c>
       <c r="R50" t="n">
-        <v>1118.570133</v>
+        <v>1118.57021</v>
       </c>
       <c r="S50" t="n">
-        <v>1357.383042</v>
+        <v>1357.383191</v>
       </c>
       <c r="T50" t="n">
-        <v>1624.610148</v>
+        <v>1624.610433</v>
       </c>
       <c r="U50" t="n">
-        <v>1915.341397</v>
+        <v>1915.341944</v>
       </c>
       <c r="V50" t="n">
-        <v>2229.972462</v>
+        <v>2229.973546</v>
       </c>
     </row>
     <row r="51">
@@ -4250,58 +4250,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>879.718626</v>
+        <v>879.718628</v>
       </c>
       <c r="F51" t="n">
-        <v>1258.783491</v>
+        <v>1258.783496</v>
       </c>
       <c r="G51" t="n">
-        <v>1588.935455</v>
+        <v>1588.935466</v>
       </c>
       <c r="H51" t="n">
-        <v>2106.005162</v>
+        <v>2106.005182</v>
       </c>
       <c r="I51" t="n">
-        <v>2740.106981</v>
+        <v>2740.107017</v>
       </c>
       <c r="J51" t="n">
-        <v>3604.910892</v>
+        <v>3604.910957</v>
       </c>
       <c r="K51" t="n">
-        <v>4790.4704</v>
+        <v>4790.470517</v>
       </c>
       <c r="L51" t="n">
-        <v>6292.887901</v>
+        <v>6292.888103</v>
       </c>
       <c r="M51" t="n">
-        <v>8133.047384</v>
+        <v>8133.047727</v>
       </c>
       <c r="N51" t="n">
-        <v>10546.575549</v>
+        <v>10546.576154</v>
       </c>
       <c r="O51" t="n">
-        <v>13604.0748</v>
+        <v>13604.075894</v>
       </c>
       <c r="P51" t="n">
-        <v>17295.857426</v>
+        <v>17295.859398</v>
       </c>
       <c r="Q51" t="n">
-        <v>21660.756576</v>
+        <v>21660.760069</v>
       </c>
       <c r="R51" t="n">
-        <v>26663.677456</v>
+        <v>26663.683525</v>
       </c>
       <c r="S51" t="n">
-        <v>32222.135348</v>
+        <v>32222.145795</v>
       </c>
       <c r="T51" t="n">
-        <v>38215.867562</v>
+        <v>38215.885569</v>
       </c>
       <c r="U51" t="n">
-        <v>44452.227849</v>
+        <v>44452.259417</v>
       </c>
       <c r="V51" t="n">
-        <v>50941.989844</v>
+        <v>50942.047377</v>
       </c>
     </row>
     <row r="52">
@@ -4326,58 +4326,58 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>910.0536980000001</v>
+        <v>910.0536970000001</v>
       </c>
       <c r="F52" t="n">
-        <v>1179.615472</v>
+        <v>1179.615469</v>
       </c>
       <c r="G52" t="n">
-        <v>1358.267781</v>
+        <v>1358.267775</v>
       </c>
       <c r="H52" t="n">
-        <v>1687.747163</v>
+        <v>1687.747152</v>
       </c>
       <c r="I52" t="n">
-        <v>2101.033191</v>
+        <v>2101.033171</v>
       </c>
       <c r="J52" t="n">
-        <v>2687.977567</v>
+        <v>2687.97753</v>
       </c>
       <c r="K52" t="n">
-        <v>3528.399689</v>
+        <v>3528.399622</v>
       </c>
       <c r="L52" t="n">
-        <v>4631.674725</v>
+        <v>4631.674599</v>
       </c>
       <c r="M52" t="n">
-        <v>6013.890056</v>
+        <v>6013.889824</v>
       </c>
       <c r="N52" t="n">
-        <v>7851.02921</v>
+        <v>7851.028799</v>
       </c>
       <c r="O52" t="n">
-        <v>10211.077475</v>
+        <v>10211.076768</v>
       </c>
       <c r="P52" t="n">
-        <v>13115.676387</v>
+        <v>13115.675202</v>
       </c>
       <c r="Q52" t="n">
-        <v>16641.433798</v>
+        <v>16641.431815</v>
       </c>
       <c r="R52" t="n">
-        <v>20836.768188</v>
+        <v>20836.764855</v>
       </c>
       <c r="S52" t="n">
-        <v>25703.925305</v>
+        <v>25703.919669</v>
       </c>
       <c r="T52" t="n">
-        <v>31205.704531</v>
+        <v>31205.694896</v>
       </c>
       <c r="U52" t="n">
-        <v>37273.788067</v>
+        <v>37273.771311</v>
       </c>
       <c r="V52" t="n">
-        <v>43898.144656</v>
+        <v>43898.114473</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>872956.067081</v>
+        <v>872956.4304280001</v>
       </c>
       <c r="F54" t="n">
-        <v>947909.249421</v>
+        <v>947910.150762</v>
       </c>
       <c r="G54" t="n">
-        <v>1109176.314125</v>
+        <v>1109178.272472</v>
       </c>
       <c r="H54" t="n">
-        <v>1289888.544661</v>
+        <v>1289892.836716</v>
       </c>
       <c r="I54" t="n">
-        <v>1489870.26907</v>
+        <v>1489882.006598</v>
       </c>
       <c r="J54" t="n">
         <v>1761620.227521</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>155030.958519</v>
+        <v>155030.595172</v>
       </c>
       <c r="F55" t="n">
-        <v>156401.637129</v>
+        <v>156400.735788</v>
       </c>
       <c r="G55" t="n">
-        <v>172566.434875</v>
+        <v>172564.476528</v>
       </c>
       <c r="H55" t="n">
-        <v>191754.386539</v>
+        <v>191750.094484</v>
       </c>
       <c r="I55" t="n">
-        <v>213665.99313</v>
+        <v>213654.255602</v>
       </c>
       <c r="J55" t="n">
         <v>182019.024679</v>
@@ -4782,58 +4782,58 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19741.480255</v>
+        <v>19741.480884</v>
       </c>
       <c r="F58" t="n">
-        <v>26474.186132</v>
+        <v>26474.188078</v>
       </c>
       <c r="G58" t="n">
-        <v>35342.269791</v>
+        <v>35342.273747</v>
       </c>
       <c r="H58" t="n">
-        <v>45424.751647</v>
+        <v>45424.758434</v>
       </c>
       <c r="I58" t="n">
-        <v>58430.073441</v>
+        <v>58430.084293</v>
       </c>
       <c r="J58" t="n">
-        <v>73641.588068</v>
+        <v>73641.604538</v>
       </c>
       <c r="K58" t="n">
-        <v>88481.84211899999</v>
+        <v>88481.865558</v>
       </c>
       <c r="L58" t="n">
-        <v>103967.409403</v>
+        <v>103967.441889</v>
       </c>
       <c r="M58" t="n">
-        <v>119487.666647</v>
+        <v>119487.710481</v>
       </c>
       <c r="N58" t="n">
-        <v>134310.687007</v>
+        <v>134310.744566</v>
       </c>
       <c r="O58" t="n">
-        <v>147877.286257</v>
+        <v>147877.359356</v>
       </c>
       <c r="P58" t="n">
-        <v>159477.726515</v>
+        <v>159477.816804</v>
       </c>
       <c r="Q58" t="n">
-        <v>168901.528312</v>
+        <v>168901.638196</v>
       </c>
       <c r="R58" t="n">
-        <v>176368.109986</v>
+        <v>176368.24338</v>
       </c>
       <c r="S58" t="n">
-        <v>182128.319847</v>
+        <v>182128.4836</v>
       </c>
       <c r="T58" t="n">
-        <v>186146.749936</v>
+        <v>186146.954306</v>
       </c>
       <c r="U58" t="n">
-        <v>188427.486346</v>
+        <v>188427.747154</v>
       </c>
       <c r="V58" t="n">
-        <v>189152.340567</v>
+        <v>189152.684827</v>
       </c>
     </row>
     <row r="59">
@@ -4858,58 +4858,58 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18513.822314</v>
+        <v>18513.824262</v>
       </c>
       <c r="F59" t="n">
-        <v>25839.5289</v>
+        <v>25839.534899</v>
       </c>
       <c r="G59" t="n">
-        <v>35739.327668</v>
+        <v>35739.341034</v>
       </c>
       <c r="H59" t="n">
-        <v>46558.328299</v>
+        <v>46558.353377</v>
       </c>
       <c r="I59" t="n">
-        <v>60181.832014</v>
+        <v>60181.875927</v>
       </c>
       <c r="J59" t="n">
-        <v>76367.890636</v>
+        <v>76367.96338099999</v>
       </c>
       <c r="K59" t="n">
-        <v>92942.77299100001</v>
+        <v>92942.885799</v>
       </c>
       <c r="L59" t="n">
-        <v>111626.362493</v>
+        <v>111626.532147</v>
       </c>
       <c r="M59" t="n">
-        <v>132700.630863</v>
+        <v>132700.880212</v>
       </c>
       <c r="N59" t="n">
-        <v>156265.256102</v>
+        <v>156265.616152</v>
       </c>
       <c r="O59" t="n">
-        <v>182252.132233</v>
+        <v>182252.645241</v>
       </c>
       <c r="P59" t="n">
-        <v>209662.673522</v>
+        <v>209663.395009</v>
       </c>
       <c r="Q59" t="n">
-        <v>237867.155602</v>
+        <v>237868.161355</v>
       </c>
       <c r="R59" t="n">
-        <v>267093.714819</v>
+        <v>267095.114761</v>
       </c>
       <c r="S59" t="n">
-        <v>297880.952047</v>
+        <v>297882.912264</v>
       </c>
       <c r="T59" t="n">
-        <v>330680.806358</v>
+        <v>330683.586857</v>
       </c>
       <c r="U59" t="n">
-        <v>365690.20855</v>
+        <v>365694.237079</v>
       </c>
       <c r="V59" t="n">
-        <v>403323.576029</v>
+        <v>403329.6234</v>
       </c>
     </row>
     <row r="60">
@@ -4934,58 +4934,58 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14913.07712</v>
+        <v>14913.078154</v>
       </c>
       <c r="F60" t="n">
-        <v>16437.502952</v>
+        <v>16437.505669</v>
       </c>
       <c r="G60" t="n">
-        <v>18043.026541</v>
+        <v>18043.031586</v>
       </c>
       <c r="H60" t="n">
-        <v>20063.236551</v>
+        <v>20063.244834</v>
       </c>
       <c r="I60" t="n">
-        <v>23422.337261</v>
+        <v>23422.35046</v>
       </c>
       <c r="J60" t="n">
-        <v>27742.02895</v>
+        <v>27742.049313</v>
       </c>
       <c r="K60" t="n">
-        <v>31672.339001</v>
+        <v>31672.368493</v>
       </c>
       <c r="L60" t="n">
-        <v>35462.91066</v>
+        <v>35462.951866</v>
       </c>
       <c r="M60" t="n">
-        <v>38661.551074</v>
+        <v>38661.606607</v>
       </c>
       <c r="N60" t="n">
-        <v>41184.175639</v>
+        <v>41184.248317</v>
       </c>
       <c r="O60" t="n">
-        <v>43090.703319</v>
+        <v>43090.796426</v>
       </c>
       <c r="P60" t="n">
-        <v>44559.166638</v>
+        <v>44559.28437</v>
       </c>
       <c r="Q60" t="n">
-        <v>45468.41514</v>
+        <v>45468.562686</v>
       </c>
       <c r="R60" t="n">
-        <v>45919.974548</v>
+        <v>45920.159142</v>
       </c>
       <c r="S60" t="n">
-        <v>45935.08041</v>
+        <v>45935.312223</v>
       </c>
       <c r="T60" t="n">
-        <v>45552.455235</v>
+        <v>45552.749159</v>
       </c>
       <c r="U60" t="n">
-        <v>44853.566782</v>
+        <v>44853.946399</v>
       </c>
       <c r="V60" t="n">
-        <v>43921.471145</v>
+        <v>43921.977998</v>
       </c>
     </row>
     <row r="61">
@@ -5010,58 +5010,58 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38923.203246</v>
+        <v>38923.203055</v>
       </c>
       <c r="F61" t="n">
-        <v>52048.353893</v>
+        <v>52048.353695</v>
       </c>
       <c r="G61" t="n">
-        <v>65971.871367</v>
+        <v>65971.87156699999</v>
       </c>
       <c r="H61" t="n">
-        <v>80008.67032200001</v>
+        <v>80008.671671</v>
       </c>
       <c r="I61" t="n">
-        <v>97731.700645</v>
+        <v>97731.704102</v>
       </c>
       <c r="J61" t="n">
-        <v>118843.950096</v>
+        <v>118843.956629</v>
       </c>
       <c r="K61" t="n">
-        <v>139359.025376</v>
+        <v>139359.035881</v>
       </c>
       <c r="L61" t="n">
-        <v>160716.997642</v>
+        <v>160717.013883</v>
       </c>
       <c r="M61" t="n">
-        <v>181866.247192</v>
+        <v>181866.271423</v>
       </c>
       <c r="N61" t="n">
-        <v>202720.328112</v>
+        <v>202720.361216</v>
       </c>
       <c r="O61" t="n">
-        <v>222755.863782</v>
+        <v>222755.90443</v>
       </c>
       <c r="P61" t="n">
-        <v>240345.384068</v>
+        <v>240345.430284</v>
       </c>
       <c r="Q61" t="n">
-        <v>254468.707489</v>
+        <v>254468.758648</v>
       </c>
       <c r="R61" t="n">
-        <v>265145.322258</v>
+        <v>265145.380242</v>
       </c>
       <c r="S61" t="n">
-        <v>272381.778832</v>
+        <v>272381.85009</v>
       </c>
       <c r="T61" t="n">
-        <v>276488.703039</v>
+        <v>276488.797537</v>
       </c>
       <c r="U61" t="n">
-        <v>277985.768481</v>
+        <v>277985.898393</v>
       </c>
       <c r="V61" t="n">
-        <v>277323.542619</v>
+        <v>277323.727865</v>
       </c>
     </row>
     <row r="62">
@@ -5086,58 +5086,58 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>73036.887191</v>
+        <v>73036.882062</v>
       </c>
       <c r="F62" t="n">
-        <v>104337.577322</v>
+        <v>104337.557648</v>
       </c>
       <c r="G62" t="n">
-        <v>137238.840164</v>
+        <v>137238.792408</v>
       </c>
       <c r="H62" t="n">
-        <v>167002.072111</v>
+        <v>167001.982222</v>
       </c>
       <c r="I62" t="n">
-        <v>199494.468529</v>
+        <v>199494.31729</v>
       </c>
       <c r="J62" t="n">
-        <v>232623.687508</v>
+        <v>232623.451917</v>
       </c>
       <c r="K62" t="n">
-        <v>258163.441929</v>
+        <v>258163.104491</v>
       </c>
       <c r="L62" t="n">
-        <v>280947.36652</v>
+        <v>280946.901572</v>
       </c>
       <c r="M62" t="n">
-        <v>299666.511848</v>
+        <v>299665.889937</v>
       </c>
       <c r="N62" t="n">
-        <v>312730.824808</v>
+        <v>312730.014772</v>
       </c>
       <c r="O62" t="n">
-        <v>320074.062396</v>
+        <v>320073.029868</v>
       </c>
       <c r="P62" t="n">
-        <v>321732.899925</v>
+        <v>321731.608239</v>
       </c>
       <c r="Q62" t="n">
-        <v>319292.316693</v>
+        <v>319290.717938</v>
       </c>
       <c r="R62" t="n">
-        <v>314449.488458</v>
+        <v>314447.513545</v>
       </c>
       <c r="S62" t="n">
-        <v>308876.97147</v>
+        <v>308874.501865</v>
       </c>
       <c r="T62" t="n">
-        <v>302383.700359</v>
+        <v>302380.56007</v>
       </c>
       <c r="U62" t="n">
-        <v>294272.549628</v>
+        <v>294268.481814</v>
       </c>
       <c r="V62" t="n">
-        <v>284983.235885</v>
+        <v>284977.796228</v>
       </c>
     </row>
     <row r="63">
@@ -5162,58 +5162,58 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>64785.626635</v>
+        <v>64785.625068</v>
       </c>
       <c r="F63" t="n">
-        <v>89902.467882</v>
+        <v>89902.46273499999</v>
       </c>
       <c r="G63" t="n">
-        <v>114151.032041</v>
+        <v>114151.02206</v>
       </c>
       <c r="H63" t="n">
-        <v>138086.676689</v>
+        <v>138086.660492</v>
       </c>
       <c r="I63" t="n">
-        <v>169302.810197</v>
+        <v>169302.783586</v>
       </c>
       <c r="J63" t="n">
-        <v>208491.694656</v>
+        <v>208491.648573</v>
       </c>
       <c r="K63" t="n">
-        <v>249435.107425</v>
+        <v>249435.02786</v>
       </c>
       <c r="L63" t="n">
-        <v>293515.740649</v>
+        <v>293515.609204</v>
       </c>
       <c r="M63" t="n">
-        <v>336774.101788</v>
+        <v>336773.898899</v>
       </c>
       <c r="N63" t="n">
-        <v>376007.18162</v>
+        <v>376006.886582</v>
       </c>
       <c r="O63" t="n">
-        <v>410346.831057</v>
+        <v>410346.418723</v>
       </c>
       <c r="P63" t="n">
-        <v>438256.296548</v>
+        <v>438255.737595</v>
       </c>
       <c r="Q63" t="n">
-        <v>459917.685089</v>
+        <v>459916.942943</v>
       </c>
       <c r="R63" t="n">
-        <v>477334.676285</v>
+        <v>477333.696486</v>
       </c>
       <c r="S63" t="n">
-        <v>491019.820221</v>
+        <v>491018.528677</v>
       </c>
       <c r="T63" t="n">
-        <v>500571.230928</v>
+        <v>500569.523141</v>
       </c>
       <c r="U63" t="n">
-        <v>505659.209203</v>
+        <v>505656.924218</v>
       </c>
       <c r="V63" t="n">
-        <v>506285.430444</v>
+        <v>506282.301457</v>
       </c>
     </row>
     <row r="64">
@@ -5238,58 +5238,58 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5691.62215</v>
+        <v>5691.622709</v>
       </c>
       <c r="F64" t="n">
-        <v>6934.796511</v>
+        <v>6934.798025</v>
       </c>
       <c r="G64" t="n">
-        <v>8421.841219</v>
+        <v>8421.844193000001</v>
       </c>
       <c r="H64" t="n">
-        <v>9974.267599000001</v>
+        <v>9974.27268</v>
       </c>
       <c r="I64" t="n">
-        <v>12042.162678</v>
+        <v>12042.170984</v>
       </c>
       <c r="J64" t="n">
-        <v>14487.641586</v>
+        <v>14487.654609</v>
       </c>
       <c r="K64" t="n">
-        <v>16687.450591</v>
+        <v>16687.469674</v>
       </c>
       <c r="L64" t="n">
-        <v>18882.07541</v>
+        <v>18882.10242</v>
       </c>
       <c r="M64" t="n">
-        <v>20946.615236</v>
+        <v>20946.652276</v>
       </c>
       <c r="N64" t="n">
-        <v>22909.311268</v>
+        <v>22909.360949</v>
       </c>
       <c r="O64" t="n">
-        <v>24739.674571</v>
+        <v>24739.740117</v>
       </c>
       <c r="P64" t="n">
-        <v>26323.828744</v>
+        <v>26323.913984</v>
       </c>
       <c r="Q64" t="n">
-        <v>27550.954805</v>
+        <v>27551.064395</v>
       </c>
       <c r="R64" t="n">
-        <v>28482.27486</v>
+        <v>28482.415275</v>
       </c>
       <c r="S64" t="n">
-        <v>29211.94851</v>
+        <v>29212.129292</v>
       </c>
       <c r="T64" t="n">
-        <v>29807.105025</v>
+        <v>29807.340699</v>
       </c>
       <c r="U64" t="n">
-        <v>30304.652814</v>
+        <v>30304.966643</v>
       </c>
       <c r="V64" t="n">
-        <v>30697.173237</v>
+        <v>30697.605775</v>
       </c>
     </row>
     <row r="65">
@@ -5314,58 +5314,58 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42090.728921</v>
+        <v>42090.728467</v>
       </c>
       <c r="F65" t="n">
-        <v>61082.53915</v>
+        <v>61082.537812</v>
       </c>
       <c r="G65" t="n">
-        <v>85460.33852999999</v>
+        <v>85460.335223</v>
       </c>
       <c r="H65" t="n">
-        <v>114509.148425</v>
+        <v>114509.141526</v>
       </c>
       <c r="I65" t="n">
-        <v>153834.985037</v>
+        <v>153834.970989</v>
       </c>
       <c r="J65" t="n">
-        <v>204028.581715</v>
+        <v>204028.554496</v>
       </c>
       <c r="K65" t="n">
-        <v>259984.37236</v>
+        <v>259984.323274</v>
       </c>
       <c r="L65" t="n">
-        <v>326539.461401</v>
+        <v>326539.37627</v>
       </c>
       <c r="M65" t="n">
-        <v>404081.220493</v>
+        <v>404081.074602</v>
       </c>
       <c r="N65" t="n">
-        <v>491736.7771</v>
+        <v>491736.530183</v>
       </c>
       <c r="O65" t="n">
-        <v>588777.680635</v>
+        <v>588777.272096</v>
       </c>
       <c r="P65" t="n">
-        <v>692728.801096</v>
+        <v>692728.1435670001</v>
       </c>
       <c r="Q65" t="n">
-        <v>802542.136631</v>
+        <v>802541.104071</v>
       </c>
       <c r="R65" t="n">
-        <v>919125.654833</v>
+        <v>919124.063081</v>
       </c>
       <c r="S65" t="n">
-        <v>1043014.168088</v>
+        <v>1043011.742569</v>
       </c>
       <c r="T65" t="n">
-        <v>1174100.929045</v>
+        <v>1174097.235895</v>
       </c>
       <c r="U65" t="n">
-        <v>1311136.632615</v>
+        <v>1311130.945199</v>
       </c>
       <c r="V65" t="n">
-        <v>1454663.107432</v>
+        <v>1454654.099384</v>
       </c>
     </row>
     <row r="66">
@@ -5390,58 +5390,58 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>32569.154445</v>
+        <v>32569.157124</v>
       </c>
       <c r="F66" t="n">
-        <v>46120.177683</v>
+        <v>46120.186077</v>
       </c>
       <c r="G66" t="n">
-        <v>63021.06586</v>
+        <v>63021.084326</v>
       </c>
       <c r="H66" t="n">
-        <v>82497.677639</v>
+        <v>82497.712405</v>
       </c>
       <c r="I66" t="n">
-        <v>108362.160549</v>
+        <v>108362.222196</v>
       </c>
       <c r="J66" t="n">
-        <v>140553.015474</v>
+        <v>140553.11943</v>
       </c>
       <c r="K66" t="n">
-        <v>174983.897525</v>
+        <v>174984.061757</v>
       </c>
       <c r="L66" t="n">
-        <v>214776.592051</v>
+        <v>214776.843411</v>
       </c>
       <c r="M66" t="n">
-        <v>260531.761581</v>
+        <v>260532.136357</v>
       </c>
       <c r="N66" t="n">
-        <v>312420.546571</v>
+        <v>312421.093076</v>
       </c>
       <c r="O66" t="n">
-        <v>370539.203636</v>
+        <v>370539.987227</v>
       </c>
       <c r="P66" t="n">
-        <v>433613.042332</v>
+        <v>433614.149767</v>
       </c>
       <c r="Q66" t="n">
-        <v>500877.590022</v>
+        <v>500879.141517</v>
       </c>
       <c r="R66" t="n">
-        <v>572442.472877</v>
+        <v>572444.642978</v>
       </c>
       <c r="S66" t="n">
-        <v>648502.416989</v>
+        <v>648505.467099</v>
       </c>
       <c r="T66" t="n">
-        <v>729430.893556</v>
+        <v>729435.2277620001</v>
       </c>
       <c r="U66" t="n">
-        <v>815240.436923</v>
+        <v>815246.712043</v>
       </c>
       <c r="V66" t="n">
-        <v>906684.734067</v>
+        <v>906694.124524</v>
       </c>
     </row>
     <row r="67">
@@ -5466,58 +5466,58 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3740.397095</v>
+        <v>3740.397266</v>
       </c>
       <c r="F67" t="n">
-        <v>5417.517065</v>
+        <v>5417.517578</v>
       </c>
       <c r="G67" t="n">
-        <v>7749.18671</v>
+        <v>7749.187753</v>
       </c>
       <c r="H67" t="n">
-        <v>10604.749954</v>
+        <v>10604.751724</v>
       </c>
       <c r="I67" t="n">
-        <v>14470.199358</v>
+        <v>14470.202086</v>
       </c>
       <c r="J67" t="n">
-        <v>19409.352356</v>
+        <v>19409.35617</v>
       </c>
       <c r="K67" t="n">
-        <v>24785.204597</v>
+        <v>24785.20934</v>
       </c>
       <c r="L67" t="n">
-        <v>30954.81983</v>
+        <v>30954.825136</v>
       </c>
       <c r="M67" t="n">
-        <v>37938.891344</v>
+        <v>37938.896071</v>
       </c>
       <c r="N67" t="n">
-        <v>45735.971872</v>
+        <v>45735.973411</v>
       </c>
       <c r="O67" t="n">
-        <v>54316.876076</v>
+        <v>54316.869653</v>
       </c>
       <c r="P67" t="n">
-        <v>63540.576562</v>
+        <v>63540.554145</v>
       </c>
       <c r="Q67" t="n">
-        <v>73348.397241</v>
+        <v>73348.34599099999</v>
       </c>
       <c r="R67" t="n">
-        <v>83864.22282</v>
+        <v>83864.122739</v>
       </c>
       <c r="S67" t="n">
-        <v>95212.687611</v>
+        <v>95212.506349</v>
       </c>
       <c r="T67" t="n">
-        <v>107439.580626</v>
+        <v>107439.263235</v>
       </c>
       <c r="U67" t="n">
-        <v>120468.245467</v>
+        <v>120467.69606</v>
       </c>
       <c r="V67" t="n">
-        <v>134403.736996</v>
+        <v>134402.776197</v>
       </c>
     </row>
     <row r="68">
@@ -5542,58 +5542,58 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>14839.200908</v>
+        <v>14839.200854</v>
       </c>
       <c r="F68" t="n">
-        <v>21838.633677</v>
+        <v>21838.63299</v>
       </c>
       <c r="G68" t="n">
-        <v>32182.389096</v>
+        <v>32182.385377</v>
       </c>
       <c r="H68" t="n">
-        <v>43751.130625</v>
+        <v>43751.119714</v>
       </c>
       <c r="I68" t="n">
-        <v>56895.760718</v>
+        <v>56895.736858</v>
       </c>
       <c r="J68" t="n">
-        <v>70258.874908</v>
+        <v>70258.831921</v>
       </c>
       <c r="K68" t="n">
-        <v>81334.402229</v>
+        <v>81334.33504599999</v>
       </c>
       <c r="L68" t="n">
-        <v>91653.741339</v>
+        <v>91653.64313300001</v>
       </c>
       <c r="M68" t="n">
-        <v>101108.335495</v>
+        <v>101108.197489</v>
       </c>
       <c r="N68" t="n">
-        <v>109324.636489</v>
+        <v>109324.447954</v>
       </c>
       <c r="O68" t="n">
-        <v>116368.363018</v>
+        <v>116368.110596</v>
       </c>
       <c r="P68" t="n">
-        <v>122122.563132</v>
+        <v>122122.229372</v>
       </c>
       <c r="Q68" t="n">
-        <v>126700.178746</v>
+        <v>126699.74075</v>
       </c>
       <c r="R68" t="n">
-        <v>130291.604276</v>
+        <v>130291.031676</v>
       </c>
       <c r="S68" t="n">
-        <v>132975.627201</v>
+        <v>132974.877982</v>
       </c>
       <c r="T68" t="n">
-        <v>134972.526536</v>
+        <v>134971.534445</v>
       </c>
       <c r="U68" t="n">
-        <v>136381.058556</v>
+        <v>136379.714427</v>
       </c>
       <c r="V68" t="n">
-        <v>137343.918591</v>
+        <v>137342.030492</v>
       </c>
     </row>
     <row r="69">
@@ -5618,58 +5618,58 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9869.673242999999</v>
+        <v>9869.674161000001</v>
       </c>
       <c r="F69" t="n">
-        <v>13096.74695</v>
+        <v>13096.749644</v>
       </c>
       <c r="G69" t="n">
-        <v>16730.248515</v>
+        <v>16730.254071</v>
       </c>
       <c r="H69" t="n">
-        <v>20381.552658</v>
+        <v>20381.562425</v>
       </c>
       <c r="I69" t="n">
-        <v>25012.616975</v>
+        <v>25012.633215</v>
       </c>
       <c r="J69" t="n">
-        <v>30744.434827</v>
+        <v>30744.460807</v>
       </c>
       <c r="K69" t="n">
-        <v>36535.143765</v>
+        <v>36535.182913</v>
       </c>
       <c r="L69" t="n">
-        <v>42593.250122</v>
+        <v>42593.307009</v>
       </c>
       <c r="M69" t="n">
-        <v>48282.7995</v>
+        <v>48282.879026</v>
       </c>
       <c r="N69" t="n">
-        <v>53247.125017</v>
+        <v>53247.232487</v>
       </c>
       <c r="O69" t="n">
-        <v>57381.541194</v>
+        <v>57381.682724</v>
       </c>
       <c r="P69" t="n">
-        <v>60530.322668</v>
+        <v>60530.505296</v>
       </c>
       <c r="Q69" t="n">
-        <v>62525.530058</v>
+        <v>62525.762133</v>
       </c>
       <c r="R69" t="n">
-        <v>63598.411715</v>
+        <v>63598.704824</v>
       </c>
       <c r="S69" t="n">
-        <v>63956.736689</v>
+        <v>63957.107515</v>
       </c>
       <c r="T69" t="n">
-        <v>63777.930966</v>
+        <v>63778.404498</v>
       </c>
       <c r="U69" t="n">
-        <v>63192.716849</v>
+        <v>63193.332774</v>
       </c>
       <c r="V69" t="n">
-        <v>62269.526984</v>
+        <v>62270.354614</v>
       </c>
     </row>
     <row r="70">
@@ -5694,58 +5694,58 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16491.572991</v>
+        <v>16491.574579</v>
       </c>
       <c r="F70" t="n">
-        <v>22500.17919</v>
+        <v>22500.183964</v>
       </c>
       <c r="G70" t="n">
-        <v>29693.467697</v>
+        <v>29693.477818</v>
       </c>
       <c r="H70" t="n">
-        <v>37301.213155</v>
+        <v>37301.231403</v>
       </c>
       <c r="I70" t="n">
-        <v>46983.060985</v>
+        <v>46983.091976</v>
       </c>
       <c r="J70" t="n">
-        <v>58534.447196</v>
+        <v>58534.497301</v>
       </c>
       <c r="K70" t="n">
-        <v>70099.477426</v>
+        <v>70099.553351</v>
       </c>
       <c r="L70" t="n">
-        <v>82892.162375</v>
+        <v>82892.27389300001</v>
       </c>
       <c r="M70" t="n">
-        <v>96594.496119</v>
+        <v>96594.655392</v>
       </c>
       <c r="N70" t="n">
-        <v>110367.157966</v>
+        <v>110367.379198</v>
       </c>
       <c r="O70" t="n">
-        <v>123868.783048</v>
+        <v>123869.083893</v>
       </c>
       <c r="P70" t="n">
-        <v>136774.85083</v>
+        <v>136775.25345</v>
       </c>
       <c r="Q70" t="n">
-        <v>149042.059672</v>
+        <v>149042.59373</v>
       </c>
       <c r="R70" t="n">
-        <v>160923.841263</v>
+        <v>160924.548912</v>
       </c>
       <c r="S70" t="n">
-        <v>172430.702187</v>
+        <v>172431.644247</v>
       </c>
       <c r="T70" t="n">
-        <v>183455.376178</v>
+        <v>183456.643145</v>
       </c>
       <c r="U70" t="n">
-        <v>193879.245084</v>
+        <v>193880.979773</v>
       </c>
       <c r="V70" t="n">
-        <v>203518.628427</v>
+        <v>203521.079234</v>
       </c>
     </row>
     <row r="71">
@@ -5770,58 +5770,58 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37061.992232</v>
+        <v>37061.992689</v>
       </c>
       <c r="F71" t="n">
-        <v>55538.276336</v>
+        <v>55538.277044</v>
       </c>
       <c r="G71" t="n">
-        <v>73894.50062799999</v>
+        <v>73894.50170399999</v>
       </c>
       <c r="H71" t="n">
-        <v>90755.35949800001</v>
+        <v>90755.36199</v>
       </c>
       <c r="I71" t="n">
-        <v>110525.191912</v>
+        <v>110525.197478</v>
       </c>
       <c r="J71" t="n">
-        <v>133817.256892</v>
+        <v>133817.267021</v>
       </c>
       <c r="K71" t="n">
-        <v>157440.133519</v>
+        <v>157440.148509</v>
       </c>
       <c r="L71" t="n">
-        <v>184990.10729</v>
+        <v>184990.125496</v>
       </c>
       <c r="M71" t="n">
-        <v>214185.907112</v>
+        <v>214185.926008</v>
       </c>
       <c r="N71" t="n">
-        <v>242207.564124</v>
+        <v>242207.581153</v>
       </c>
       <c r="O71" t="n">
-        <v>266322.017258</v>
+        <v>266322.032004</v>
       </c>
       <c r="P71" t="n">
-        <v>284788.625898</v>
+        <v>284788.640435</v>
       </c>
       <c r="Q71" t="n">
-        <v>297608.84161</v>
+        <v>297608.860894</v>
       </c>
       <c r="R71" t="n">
-        <v>306701.985297</v>
+        <v>306702.014151</v>
       </c>
       <c r="S71" t="n">
-        <v>312840.209884</v>
+        <v>312840.255321</v>
       </c>
       <c r="T71" t="n">
-        <v>315948.04984</v>
+        <v>315948.12271</v>
       </c>
       <c r="U71" t="n">
-        <v>315913.163796</v>
+        <v>315913.2805</v>
       </c>
       <c r="V71" t="n">
-        <v>312960.374682</v>
+        <v>312960.565851</v>
       </c>
     </row>
     <row r="72">
@@ -5846,58 +5846,58 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21812.391623</v>
+        <v>21812.392116</v>
       </c>
       <c r="F72" t="n">
-        <v>27496.82575</v>
+        <v>27496.827288</v>
       </c>
       <c r="G72" t="n">
-        <v>33783.238935</v>
+        <v>33783.242029</v>
       </c>
       <c r="H72" t="n">
-        <v>40151.724265</v>
+        <v>40151.729476</v>
       </c>
       <c r="I72" t="n">
-        <v>48669.219469</v>
+        <v>48669.227472</v>
       </c>
       <c r="J72" t="n">
-        <v>59041.681578</v>
+        <v>59041.69287</v>
       </c>
       <c r="K72" t="n">
-        <v>69222.36563099999</v>
+        <v>69222.380005</v>
       </c>
       <c r="L72" t="n">
-        <v>80090.139018</v>
+        <v>80090.155956</v>
       </c>
       <c r="M72" t="n">
-        <v>90987.08905900001</v>
+        <v>90987.107369</v>
       </c>
       <c r="N72" t="n">
-        <v>100854.28732</v>
+        <v>100854.305444</v>
       </c>
       <c r="O72" t="n">
-        <v>109416.242532</v>
+        <v>109416.258972</v>
       </c>
       <c r="P72" t="n">
-        <v>117022.562944</v>
+        <v>117022.573997</v>
       </c>
       <c r="Q72" t="n">
-        <v>123940.657553</v>
+        <v>123940.657106</v>
       </c>
       <c r="R72" t="n">
-        <v>130289.558539</v>
+        <v>130289.538359</v>
       </c>
       <c r="S72" t="n">
-        <v>135867.129002</v>
+        <v>135867.079105</v>
       </c>
       <c r="T72" t="n">
-        <v>140619.881614</v>
+        <v>140619.787228</v>
       </c>
       <c r="U72" t="n">
-        <v>144605.551273</v>
+        <v>144605.387799</v>
       </c>
       <c r="V72" t="n">
-        <v>147802.258676</v>
+        <v>147801.986363</v>
       </c>
     </row>
     <row r="73">
@@ -5922,58 +5922,58 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>34452.062758</v>
+        <v>34452.059067</v>
       </c>
       <c r="F73" t="n">
-        <v>36045.356206</v>
+        <v>36045.35045</v>
       </c>
       <c r="G73" t="n">
-        <v>33617.903074</v>
+        <v>33617.898702</v>
       </c>
       <c r="H73" t="n">
-        <v>32025.476898</v>
+        <v>32025.474637</v>
       </c>
       <c r="I73" t="n">
-        <v>34124.233621</v>
+        <v>34124.232661</v>
       </c>
       <c r="J73" t="n">
-        <v>38926.101462</v>
+        <v>38926.100684</v>
       </c>
       <c r="K73" t="n">
-        <v>44247.288642</v>
+        <v>44247.286631</v>
       </c>
       <c r="L73" t="n">
-        <v>49665.60703</v>
+        <v>49665.602586</v>
       </c>
       <c r="M73" t="n">
-        <v>54357.735417</v>
+        <v>54357.727635</v>
       </c>
       <c r="N73" t="n">
-        <v>58025.729513</v>
+        <v>58025.717398</v>
       </c>
       <c r="O73" t="n">
-        <v>60796.623832</v>
+        <v>60796.605642</v>
       </c>
       <c r="P73" t="n">
-        <v>62674.232281</v>
+        <v>62674.205228</v>
       </c>
       <c r="Q73" t="n">
-        <v>63669.741029</v>
+        <v>63669.701716</v>
       </c>
       <c r="R73" t="n">
-        <v>63904.984384</v>
+        <v>63904.92918</v>
       </c>
       <c r="S73" t="n">
-        <v>63563.511238</v>
+        <v>63563.436025</v>
       </c>
       <c r="T73" t="n">
-        <v>62767.606119</v>
+        <v>62767.50521</v>
       </c>
       <c r="U73" t="n">
-        <v>61625.770342</v>
+        <v>61625.634098</v>
       </c>
       <c r="V73" t="n">
-        <v>60274.769502</v>
+        <v>60274.579358</v>
       </c>
     </row>
     <row r="74">
@@ -5998,58 +5998,58 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5928.196874</v>
+        <v>5928.197484</v>
       </c>
       <c r="F74" t="n">
-        <v>8965.823700000001</v>
+        <v>8965.825704000001</v>
       </c>
       <c r="G74" t="n">
-        <v>11826.631264</v>
+        <v>11826.635503</v>
       </c>
       <c r="H74" t="n">
-        <v>14190.962763</v>
+        <v>14190.970089</v>
       </c>
       <c r="I74" t="n">
-        <v>16883.108713</v>
+        <v>16883.120527</v>
       </c>
       <c r="J74" t="n">
-        <v>19985.744193</v>
+        <v>19985.762441</v>
       </c>
       <c r="K74" t="n">
-        <v>22847.009973</v>
+        <v>22847.036518</v>
       </c>
       <c r="L74" t="n">
-        <v>25713.249769</v>
+        <v>25713.28713</v>
       </c>
       <c r="M74" t="n">
-        <v>28397.665232</v>
+        <v>28397.716216</v>
       </c>
       <c r="N74" t="n">
-        <v>30729.829472</v>
+        <v>30729.897144</v>
       </c>
       <c r="O74" t="n">
-        <v>32630.115455</v>
+        <v>32630.203333</v>
       </c>
       <c r="P74" t="n">
-        <v>34021.527395</v>
+        <v>34021.639557</v>
       </c>
       <c r="Q74" t="n">
-        <v>34914.331908</v>
+        <v>34914.473532</v>
       </c>
       <c r="R74" t="n">
-        <v>35449.486383</v>
+        <v>35449.664869</v>
       </c>
       <c r="S74" t="n">
-        <v>35704.059453</v>
+        <v>35704.285456</v>
       </c>
       <c r="T74" t="n">
-        <v>35739.429118</v>
+        <v>35739.71858</v>
       </c>
       <c r="U74" t="n">
-        <v>35610.986884</v>
+        <v>35611.36522</v>
       </c>
       <c r="V74" t="n">
-        <v>35347.226354</v>
+        <v>35347.738073</v>
       </c>
     </row>
     <row r="75">
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29627.343049</v>
+        <v>29627.270483</v>
       </c>
       <c r="F75" t="n">
-        <v>37521.778567</v>
+        <v>37521.430789</v>
       </c>
       <c r="G75" t="n">
-        <v>45441.86628</v>
+        <v>45440.498336</v>
       </c>
       <c r="H75" t="n">
-        <v>54580.866448</v>
+        <v>54576.701873</v>
       </c>
       <c r="I75" t="n">
-        <v>64006.798286</v>
+        <v>63993.296305</v>
       </c>
       <c r="J75" t="n">
         <v>97354.174558</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>93861.8158</v>
+        <v>93857.32713000001</v>
       </c>
       <c r="F76" t="n">
-        <v>122571.496172</v>
+        <v>122556.311531</v>
       </c>
       <c r="G76" t="n">
-        <v>121290.710056</v>
+        <v>121259.497348</v>
       </c>
       <c r="H76" t="n">
-        <v>124010.410941</v>
+        <v>123945.487839</v>
       </c>
       <c r="I76" t="n">
-        <v>135024.399897</v>
+        <v>134850.000155</v>
       </c>
       <c r="J76" t="n">
         <v>457139.613246</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>41153.443109</v>
+        <v>41153.322805</v>
       </c>
       <c r="F77" t="n">
-        <v>59187.51001</v>
+        <v>59186.86355</v>
       </c>
       <c r="G77" t="n">
-        <v>75257.37605200001</v>
+        <v>75254.828459</v>
       </c>
       <c r="H77" t="n">
-        <v>87930.615517</v>
+        <v>87923.259426</v>
       </c>
       <c r="I77" t="n">
-        <v>95749.93590500001</v>
+        <v>95728.180714</v>
       </c>
       <c r="J77" t="n">
         <v>136432.324422</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>349036.837121</v>
+        <v>349036.613507</v>
       </c>
       <c r="F78" t="n">
-        <v>383960.372038</v>
+        <v>383958.789354</v>
       </c>
       <c r="G78" t="n">
-        <v>394401.70311</v>
+        <v>394394.421306</v>
       </c>
       <c r="H78" t="n">
-        <v>428438.310985</v>
+        <v>428416.331605</v>
       </c>
       <c r="I78" t="n">
-        <v>483927.750627</v>
+        <v>483856.627077</v>
       </c>
       <c r="J78" t="n">
         <v>684837.642113</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>49483.864083</v>
+        <v>49484.608626</v>
       </c>
       <c r="F79" t="n">
-        <v>81958.61693800001</v>
+        <v>81961.464725</v>
       </c>
       <c r="G79" t="n">
-        <v>129663.263933</v>
+        <v>129670.801796</v>
       </c>
       <c r="H79" t="n">
-        <v>191350.647937</v>
+        <v>191369.708823</v>
       </c>
       <c r="I79" t="n">
-        <v>257846.416835</v>
+        <v>257903.90589</v>
       </c>
       <c r="J79" t="n">
         <v>212692.944008</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>20938.352802</v>
+        <v>20938.571674</v>
       </c>
       <c r="F80" t="n">
-        <v>22603.510959</v>
+        <v>22604.050388</v>
       </c>
       <c r="G80" t="n">
-        <v>23670.054886</v>
+        <v>23670.94503</v>
       </c>
       <c r="H80" t="n">
-        <v>26921.833771</v>
+        <v>26923.455545</v>
       </c>
       <c r="I80" t="n">
-        <v>31981.89836</v>
+        <v>31985.972717</v>
       </c>
       <c r="J80" t="n">
         <v>31188.312648</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>65173.719161</v>
+        <v>65174.823334</v>
       </c>
       <c r="F81" t="n">
-        <v>112077.505323</v>
+        <v>112081.940233</v>
       </c>
       <c r="G81" t="n">
-        <v>181356.794374</v>
+        <v>181369.122321</v>
       </c>
       <c r="H81" t="n">
-        <v>274517.357107</v>
+        <v>274550.165837</v>
       </c>
       <c r="I81" t="n">
-        <v>381537.888734</v>
+        <v>381641.885463</v>
       </c>
       <c r="J81" t="n">
         <v>287770.138361</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>85589.352058</v>
+        <v>85589.947142</v>
       </c>
       <c r="F82" t="n">
-        <v>109147.808182</v>
+        <v>109149.409174</v>
       </c>
       <c r="G82" t="n">
-        <v>128659.306072</v>
+        <v>128661.698648</v>
       </c>
       <c r="H82" t="n">
-        <v>155544.641579</v>
+        <v>155548.007852</v>
       </c>
       <c r="I82" t="n">
-        <v>187761.877084</v>
+        <v>187767.752642</v>
       </c>
       <c r="J82" t="n">
         <v>214143.280013</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>218051.207817</v>
+        <v>218053.450298</v>
       </c>
       <c r="F83" t="n">
-        <v>369955.326816</v>
+        <v>369963.665258</v>
       </c>
       <c r="G83" t="n">
-        <v>577858.044627</v>
+        <v>577877.306144</v>
       </c>
       <c r="H83" t="n">
-        <v>836276.489173</v>
+        <v>836318.054658</v>
       </c>
       <c r="I83" t="n">
-        <v>1105207.429038</v>
+        <v>1105316.773803</v>
       </c>
       <c r="J83" t="n">
         <v>1158264.276542</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>166067.072632</v>
+        <v>166067.996128</v>
       </c>
       <c r="F86" t="n">
-        <v>184267.356449</v>
+        <v>184269.972275</v>
       </c>
       <c r="G86" t="n">
-        <v>213518.38292</v>
+        <v>213524.553877</v>
       </c>
       <c r="H86" t="n">
-        <v>245983.684304</v>
+        <v>245998.043877</v>
       </c>
       <c r="I86" t="n">
-        <v>278118.344857</v>
+        <v>278158.942914</v>
       </c>
       <c r="J86" t="n">
         <v>143208.077014</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15455.590335</v>
+        <v>15455.528913</v>
       </c>
       <c r="F87" t="n">
-        <v>19298.134726</v>
+        <v>19297.944026</v>
       </c>
       <c r="G87" t="n">
-        <v>25718.217072</v>
+        <v>25717.710534</v>
       </c>
       <c r="H87" t="n">
-        <v>33353.586199</v>
+        <v>33352.276745</v>
       </c>
       <c r="I87" t="n">
-        <v>41579.205521</v>
+        <v>41575.158275</v>
       </c>
       <c r="J87" t="n">
         <v>66919.414974</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>281542.07149</v>
+        <v>281542.761108</v>
       </c>
       <c r="F88" t="n">
-        <v>284690.844357</v>
+        <v>284692.697307</v>
       </c>
       <c r="G88" t="n">
-        <v>311128.503687</v>
+        <v>311132.757333</v>
       </c>
       <c r="H88" t="n">
-        <v>355704.183486</v>
+        <v>355714.162885</v>
       </c>
       <c r="I88" t="n">
-        <v>412455.92943</v>
+        <v>412484.99312</v>
       </c>
       <c r="J88" t="n">
         <v>352218.350701</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>34583.786261</v>
+        <v>34583.93739</v>
       </c>
       <c r="F89" t="n">
-        <v>37125.368271</v>
+        <v>37125.785525</v>
       </c>
       <c r="G89" t="n">
-        <v>43679.379188</v>
+        <v>43680.382027</v>
       </c>
       <c r="H89" t="n">
-        <v>51396.126096</v>
+        <v>51398.512765</v>
       </c>
       <c r="I89" t="n">
-        <v>59453.555532</v>
+        <v>59460.457524</v>
       </c>
       <c r="J89" t="n">
         <v>38634.434939</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103479.562995</v>
+        <v>103479.093553</v>
       </c>
       <c r="F90" t="n">
-        <v>112453.668771</v>
+        <v>112452.413725</v>
       </c>
       <c r="G90" t="n">
-        <v>135104.655362</v>
+        <v>135101.668573</v>
       </c>
       <c r="H90" t="n">
-        <v>163711.759761</v>
+        <v>163704.555403</v>
       </c>
       <c r="I90" t="n">
-        <v>194611.255375</v>
+        <v>194589.99977</v>
       </c>
       <c r="J90" t="n">
         <v>311370.73144</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>14520.576607</v>
+        <v>14520.242904</v>
       </c>
       <c r="F91" t="n">
-        <v>16145.458154</v>
+        <v>16144.528007</v>
       </c>
       <c r="G91" t="n">
-        <v>18972.429471</v>
+        <v>18970.24394</v>
       </c>
       <c r="H91" t="n">
-        <v>21848.588362</v>
+        <v>21843.580703</v>
       </c>
       <c r="I91" t="n">
-        <v>24525.13237</v>
+        <v>24511.329174</v>
       </c>
       <c r="J91" t="n">
         <v>80034.527363</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>18861.713935</v>
+        <v>18861.624665</v>
       </c>
       <c r="F92" t="n">
-        <v>21136.610698</v>
+        <v>21136.362367</v>
       </c>
       <c r="G92" t="n">
-        <v>25610.482068</v>
+        <v>25609.883248</v>
       </c>
       <c r="H92" t="n">
-        <v>30245.307099</v>
+        <v>30243.902068</v>
       </c>
       <c r="I92" t="n">
-        <v>34513.570701</v>
+        <v>34509.61249</v>
       </c>
       <c r="J92" t="n">
         <v>53540.866624</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4448.657182</v>
+        <v>4448.614118</v>
       </c>
       <c r="F93" t="n">
-        <v>5240.645387</v>
+        <v>5240.51848</v>
       </c>
       <c r="G93" t="n">
-        <v>6763.843705</v>
+        <v>6763.515164</v>
       </c>
       <c r="H93" t="n">
-        <v>8746.648627</v>
+        <v>8745.796480000001</v>
       </c>
       <c r="I93" t="n">
-        <v>10984.568439</v>
+        <v>10981.906468</v>
       </c>
       <c r="J93" t="n">
         <v>24612.855117</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>560107.433568</v>
+        <v>560106.600957</v>
       </c>
       <c r="F94" t="n">
-        <v>668081.811735</v>
+        <v>668079.389323</v>
       </c>
       <c r="G94" t="n">
-        <v>820266.724504</v>
+        <v>820260.973952</v>
       </c>
       <c r="H94" t="n">
-        <v>985035.27354</v>
+        <v>985021.795428</v>
       </c>
       <c r="I94" t="n">
-        <v>1145922.760694</v>
+        <v>1145884.250891</v>
       </c>
       <c r="J94" t="n">
         <v>1441680.992004</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>224662.686871</v>
+        <v>224662.827525</v>
       </c>
       <c r="F95" t="n">
-        <v>268442.638052</v>
+        <v>268443.089242</v>
       </c>
       <c r="G95" t="n">
-        <v>334832.877463</v>
+        <v>334834.07563</v>
       </c>
       <c r="H95" t="n">
-        <v>406215.072844</v>
+        <v>406218.079165</v>
       </c>
       <c r="I95" t="n">
-        <v>475643.963127</v>
+        <v>475652.790817</v>
       </c>
       <c r="J95" t="n">
         <v>495840.65583</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>90767.575883</v>
+        <v>90767.429039</v>
       </c>
       <c r="F96" t="n">
-        <v>95954.950184</v>
+        <v>95954.59106599999</v>
       </c>
       <c r="G96" t="n">
-        <v>105618.732872</v>
+        <v>105618.009138</v>
       </c>
       <c r="H96" t="n">
-        <v>119821.883915</v>
+        <v>119820.335691</v>
       </c>
       <c r="I96" t="n">
-        <v>137113.18677</v>
+        <v>137108.900971</v>
       </c>
       <c r="J96" t="n">
         <v>172442.387051</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>50495.372243</v>
+        <v>50495.4437</v>
       </c>
       <c r="F97" t="n">
-        <v>49406.975916</v>
+        <v>49407.171356</v>
       </c>
       <c r="G97" t="n">
-        <v>52825.127388</v>
+        <v>52825.582283</v>
       </c>
       <c r="H97" t="n">
-        <v>59632.256467</v>
+        <v>59633.329489</v>
       </c>
       <c r="I97" t="n">
-        <v>68810.69788399999</v>
+        <v>68813.828287</v>
       </c>
       <c r="J97" t="n">
         <v>65730.317644</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>208541.835173</v>
+        <v>208541.444799</v>
       </c>
       <c r="F98" t="n">
-        <v>207921.466991</v>
+        <v>207920.567146</v>
       </c>
       <c r="G98" t="n">
-        <v>218188.22296</v>
+        <v>218186.492307</v>
       </c>
       <c r="H98" t="n">
-        <v>228553.28044</v>
+        <v>228549.904763</v>
       </c>
       <c r="I98" t="n">
-        <v>244533.287865</v>
+        <v>244524.765107</v>
       </c>
       <c r="J98" t="n">
         <v>275696.543496</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>231275.425164</v>
+        <v>231274.022298</v>
       </c>
       <c r="F99" t="n">
-        <v>266885.418835</v>
+        <v>266881.422451</v>
       </c>
       <c r="G99" t="n">
-        <v>328003.696625</v>
+        <v>327993.998714</v>
       </c>
       <c r="H99" t="n">
-        <v>387580.10662</v>
+        <v>387557.436837</v>
       </c>
       <c r="I99" t="n">
-        <v>450741.799228</v>
+        <v>450676.774349</v>
       </c>
       <c r="J99" t="n">
         <v>628097.270272</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>97563.000099</v>
+        <v>97562.20229299999</v>
       </c>
       <c r="F100" t="n">
-        <v>96573.46308</v>
+        <v>96571.524804</v>
       </c>
       <c r="G100" t="n">
-        <v>102646.181252</v>
+        <v>102642.136396</v>
       </c>
       <c r="H100" t="n">
-        <v>109009.170311</v>
+        <v>109000.709277</v>
       </c>
       <c r="I100" t="n">
-        <v>118028.265012</v>
+        <v>118005.739077</v>
       </c>
       <c r="J100" t="n">
         <v>166942.011167</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>231214.107993</v>
+        <v>231216.534941</v>
       </c>
       <c r="F101" t="n">
-        <v>245236.603028</v>
+        <v>245243.116541</v>
       </c>
       <c r="G101" t="n">
-        <v>277022.184643</v>
+        <v>277037.071956</v>
       </c>
       <c r="H101" t="n">
-        <v>306595.411584</v>
+        <v>306628.617255</v>
       </c>
       <c r="I101" t="n">
-        <v>339169.401532</v>
+        <v>339261.378619</v>
       </c>
       <c r="J101" t="n">
         <v>202170.507047</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1937959.445776</v>
+        <v>1937970.383902</v>
       </c>
       <c r="F102" t="n">
-        <v>2173972.209466</v>
+        <v>2174003.478573</v>
       </c>
       <c r="G102" t="n">
-        <v>2625128.447069</v>
+        <v>2625205.320238</v>
       </c>
       <c r="H102" t="n">
-        <v>3089560.849579</v>
+        <v>3089743.89655</v>
       </c>
       <c r="I102" t="n">
-        <v>3607193.81657</v>
+        <v>3607729.951081</v>
       </c>
       <c r="J102" t="n">
         <v>3079786.083031</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2165326.93955</v>
+        <v>2165334.858699</v>
       </c>
       <c r="F103" t="n">
-        <v>2080416.328458</v>
+        <v>2080436.106898</v>
       </c>
       <c r="G103" t="n">
-        <v>2122669.190171</v>
+        <v>2122711.082491</v>
       </c>
       <c r="H103" t="n">
-        <v>2176491.092609</v>
+        <v>2176579.216441</v>
       </c>
       <c r="I103" t="n">
-        <v>2291964.106905</v>
+        <v>2292199.009342</v>
       </c>
       <c r="J103" t="n">
         <v>2001527.732935</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>174699.619703</v>
+        <v>174698.164654</v>
       </c>
       <c r="F104" t="n">
-        <v>188391.029916</v>
+        <v>188387.151848</v>
       </c>
       <c r="G104" t="n">
-        <v>217052.06254</v>
+        <v>217043.229447</v>
       </c>
       <c r="H104" t="n">
-        <v>248070.780079</v>
+        <v>248050.769315</v>
       </c>
       <c r="I104" t="n">
-        <v>284799.971535</v>
+        <v>284743.19416</v>
       </c>
       <c r="J104" t="n">
         <v>424717.625699</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>95095.99426199999</v>
+        <v>95095.500914</v>
       </c>
       <c r="F105" t="n">
-        <v>104212.001479</v>
+        <v>104210.679957</v>
       </c>
       <c r="G105" t="n">
-        <v>123449.660707</v>
+        <v>123446.595257</v>
       </c>
       <c r="H105" t="n">
-        <v>142519.104234</v>
+        <v>142512.146553</v>
       </c>
       <c r="I105" t="n">
-        <v>163714.86984</v>
+        <v>163695.245444</v>
       </c>
       <c r="J105" t="n">
         <v>219299.486931</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>949173.038403</v>
+        <v>949165.751121</v>
       </c>
       <c r="F106" t="n">
-        <v>1073433.391713</v>
+        <v>1073412.988555</v>
       </c>
       <c r="G106" t="n">
-        <v>1318221.110249</v>
+        <v>1318171.43307</v>
       </c>
       <c r="H106" t="n">
-        <v>1564226.6662</v>
+        <v>1564109.634385</v>
       </c>
       <c r="I106" t="n">
-        <v>1829003.997441</v>
+        <v>1828665.554525</v>
       </c>
       <c r="J106" t="n">
         <v>2696718.901347</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4507.044718</v>
+        <v>4506.24848</v>
       </c>
       <c r="F107" t="n">
-        <v>5382.699846</v>
+        <v>5380.325907</v>
       </c>
       <c r="G107" t="n">
-        <v>6499.304455</v>
+        <v>6493.596705</v>
       </c>
       <c r="H107" t="n">
-        <v>7625.559469</v>
+        <v>7612.299691</v>
       </c>
       <c r="I107" t="n">
-        <v>9109.909607</v>
+        <v>9071.534740999999</v>
       </c>
       <c r="J107" t="n">
         <v>83437.044005</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>371553.601095</v>
+        <v>371550.24992</v>
       </c>
       <c r="F108" t="n">
-        <v>399651.798277</v>
+        <v>399642.892203</v>
       </c>
       <c r="G108" t="n">
-        <v>451205.897957</v>
+        <v>451186.04754</v>
       </c>
       <c r="H108" t="n">
-        <v>499130.057514</v>
+        <v>499086.631977</v>
       </c>
       <c r="I108" t="n">
-        <v>553933.2543340001</v>
+        <v>553814.440636</v>
       </c>
       <c r="J108" t="n">
         <v>817861.34702</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>172856.043398</v>
+        <v>172856.437495</v>
       </c>
       <c r="F109" t="n">
-        <v>186453.989766</v>
+        <v>186455.104307</v>
       </c>
       <c r="G109" t="n">
-        <v>224838.261254</v>
+        <v>224841.053247</v>
       </c>
       <c r="H109" t="n">
-        <v>272375.50647</v>
+        <v>272382.411324</v>
       </c>
       <c r="I109" t="n">
-        <v>332283.011998</v>
+        <v>332304.1818</v>
       </c>
       <c r="J109" t="n">
         <v>350535.785429</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>545962.734784</v>
+        <v>545969.521282</v>
       </c>
       <c r="F110" t="n">
-        <v>625438.557629</v>
+        <v>625458.179687</v>
       </c>
       <c r="G110" t="n">
-        <v>768777.085927</v>
+        <v>768825.7630480001</v>
       </c>
       <c r="H110" t="n">
-        <v>909073.015658</v>
+        <v>909188.810238</v>
       </c>
       <c r="I110" t="n">
-        <v>1054481.949657</v>
+        <v>1054817.934717</v>
       </c>
       <c r="J110" t="n">
         <v>557627.949198</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>936048.620652</v>
+        <v>936047.197428</v>
       </c>
       <c r="F111" t="n">
-        <v>1038836.996212</v>
+        <v>1038833.30623</v>
       </c>
       <c r="G111" t="n">
-        <v>1220164.935439</v>
+        <v>1220156.878403</v>
       </c>
       <c r="H111" t="n">
-        <v>1395902.656449</v>
+        <v>1395885.264499</v>
       </c>
       <c r="I111" t="n">
-        <v>1598256.443923</v>
+        <v>1598208.92549</v>
       </c>
       <c r="J111" t="n">
         <v>1877125.329875</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1130350.249231</v>
+        <v>1130339.181773</v>
       </c>
       <c r="F112" t="n">
-        <v>1273209.934304</v>
+        <v>1273179.043893</v>
       </c>
       <c r="G112" t="n">
-        <v>1547378.382751</v>
+        <v>1547303.925182</v>
       </c>
       <c r="H112" t="n">
-        <v>1826490.536784</v>
+        <v>1826316.044894</v>
       </c>
       <c r="I112" t="n">
-        <v>2136042.358554</v>
+        <v>2135537.814913</v>
       </c>
       <c r="J112" t="n">
         <v>3370091.906547</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>119687.004829</v>
+        <v>119678.925245</v>
       </c>
       <c r="F113" t="n">
-        <v>127100.687408</v>
+        <v>127078.910611</v>
       </c>
       <c r="G113" t="n">
-        <v>114473.48157</v>
+        <v>114432.679481</v>
       </c>
       <c r="H113" t="n">
-        <v>119752.233372</v>
+        <v>119665.553058</v>
       </c>
       <c r="I113" t="n">
-        <v>133467.76979</v>
+        <v>133235.373212</v>
       </c>
       <c r="J113" t="n">
         <v>265840.685023</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21226.548942</v>
+        <v>21226.780391</v>
       </c>
       <c r="F114" t="n">
-        <v>31783.912975</v>
+        <v>31784.825414</v>
       </c>
       <c r="G114" t="n">
-        <v>42565.384479</v>
+        <v>42567.768906</v>
       </c>
       <c r="H114" t="n">
-        <v>57840.471225</v>
+        <v>57846.758032</v>
       </c>
       <c r="I114" t="n">
-        <v>72490.24529799999</v>
+        <v>72509.00562700001</v>
       </c>
       <c r="J114" t="n">
         <v>73703.096349</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>568545.080229</v>
+        <v>568552.9283650001</v>
       </c>
       <c r="F115" t="n">
-        <v>692754.370997</v>
+        <v>692775.235356</v>
       </c>
       <c r="G115" t="n">
-        <v>778214.8113309999</v>
+        <v>778253.228993</v>
       </c>
       <c r="H115" t="n">
-        <v>956743.243583</v>
+        <v>956823.637091</v>
       </c>
       <c r="I115" t="n">
-        <v>1159230.992092</v>
+        <v>1159444.628341</v>
       </c>
       <c r="J115" t="n">
         <v>1241321.498808</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>21239.598905</v>
+        <v>21239.53711</v>
       </c>
       <c r="F116" t="n">
-        <v>23201.048169</v>
+        <v>23200.881652</v>
       </c>
       <c r="G116" t="n">
-        <v>26309.517782</v>
+        <v>26309.143863</v>
       </c>
       <c r="H116" t="n">
-        <v>30457.789899</v>
+        <v>30456.930287</v>
       </c>
       <c r="I116" t="n">
-        <v>33918.175229</v>
+        <v>33915.80021</v>
       </c>
       <c r="J116" t="n">
         <v>24667.047391</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>56312.201588</v>
+        <v>56312.083774</v>
       </c>
       <c r="F117" t="n">
-        <v>75973.654159</v>
+        <v>75973.27323599999</v>
       </c>
       <c r="G117" t="n">
-        <v>95005.391179</v>
+        <v>95004.463754</v>
       </c>
       <c r="H117" t="n">
-        <v>115623.815744</v>
+        <v>115621.597402</v>
       </c>
       <c r="I117" t="n">
-        <v>131717.138674</v>
+        <v>131710.907252</v>
       </c>
       <c r="J117" t="n">
         <v>111828.594182</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>40503.633472</v>
+        <v>40504.050556</v>
       </c>
       <c r="F118" t="n">
-        <v>43239.737592</v>
+        <v>43240.857863</v>
       </c>
       <c r="G118" t="n">
-        <v>47644.576407</v>
+        <v>47647.054151</v>
       </c>
       <c r="H118" t="n">
-        <v>53915.208603</v>
+        <v>53920.816533</v>
       </c>
       <c r="I118" t="n">
-        <v>59268.294619</v>
+        <v>59283.582823</v>
       </c>
       <c r="J118" t="n">
         <v>140472.673702</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20344.384288</v>
+        <v>20344.402767</v>
       </c>
       <c r="F119" t="n">
-        <v>26210.084488</v>
+        <v>26210.150269</v>
       </c>
       <c r="G119" t="n">
-        <v>34317.985809</v>
+        <v>34318.171014</v>
       </c>
       <c r="H119" t="n">
-        <v>44352.713201</v>
+        <v>44353.213906</v>
       </c>
       <c r="I119" t="n">
-        <v>53463.211541</v>
+        <v>53464.751496</v>
       </c>
       <c r="J119" t="n">
         <v>69677.64619</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>10819.937094</v>
+        <v>10819.912539</v>
       </c>
       <c r="F120" t="n">
-        <v>11897.555416</v>
+        <v>11897.489115</v>
       </c>
       <c r="G120" t="n">
-        <v>13610.37243</v>
+        <v>13610.222764</v>
       </c>
       <c r="H120" t="n">
-        <v>15933.346625</v>
+        <v>15932.999485</v>
       </c>
       <c r="I120" t="n">
-        <v>17979.26575</v>
+        <v>17978.295272</v>
       </c>
       <c r="J120" t="n">
         <v>14763.115493</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>135460.096322</v>
+        <v>135459.93806</v>
       </c>
       <c r="F121" t="n">
-        <v>172034.915424</v>
+        <v>172034.447851</v>
       </c>
       <c r="G121" t="n">
-        <v>221523.955803</v>
+        <v>221522.821433</v>
       </c>
       <c r="H121" t="n">
-        <v>278914.485495</v>
+        <v>278911.742526</v>
       </c>
       <c r="I121" t="n">
-        <v>325574.521936</v>
+        <v>325566.725081</v>
       </c>
       <c r="J121" t="n">
         <v>320821.836126</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>943266.659332</v>
+        <v>943266.586194</v>
       </c>
       <c r="F122" t="n">
-        <v>1041126.137792</v>
+        <v>1041126.033053</v>
       </c>
       <c r="G122" t="n">
-        <v>1198991.17174</v>
+        <v>1198991.094172</v>
       </c>
       <c r="H122" t="n">
-        <v>1419141.019182</v>
+        <v>1419141.07861</v>
       </c>
       <c r="I122" t="n">
-        <v>1626706.080001</v>
+        <v>1626706.625616</v>
       </c>
       <c r="J122" t="n">
         <v>1823536.183665</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>65722.136558</v>
+        <v>65743.051557</v>
       </c>
       <c r="F123" t="n">
-        <v>73158.43055999999</v>
+        <v>73213.00581800001</v>
       </c>
       <c r="G123" t="n">
-        <v>85045.351553</v>
+        <v>85163.532695</v>
       </c>
       <c r="H123" t="n">
-        <v>96633.166012</v>
+        <v>96883.420784</v>
       </c>
       <c r="I123" t="n">
-        <v>106636.565319</v>
+        <v>107264.562231</v>
       </c>
       <c r="J123" t="n">
         <v>37057.286545</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>502073.662619</v>
+        <v>502147.881673</v>
       </c>
       <c r="F124" t="n">
-        <v>562019.932552</v>
+        <v>562212.443753</v>
       </c>
       <c r="G124" t="n">
-        <v>648106.385992</v>
+        <v>648511.851703</v>
       </c>
       <c r="H124" t="n">
-        <v>735833.99075</v>
+        <v>736674.233172</v>
       </c>
       <c r="I124" t="n">
-        <v>818605.358142</v>
+        <v>820665.8848070001</v>
       </c>
       <c r="J124" t="n">
         <v>638552.14452</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>232423.044823</v>
+        <v>232327.91077</v>
       </c>
       <c r="F125" t="n">
-        <v>242440.268358</v>
+        <v>242193.181899</v>
       </c>
       <c r="G125" t="n">
-        <v>258784.317626</v>
+        <v>258260.670771</v>
       </c>
       <c r="H125" t="n">
-        <v>281137.591909</v>
+        <v>280047.094714</v>
       </c>
       <c r="I125" t="n">
-        <v>318381.980009</v>
+        <v>315693.456432</v>
       </c>
       <c r="J125" t="n">
         <v>683889.950705</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>448948.990095</v>
+        <v>448952.803759</v>
       </c>
       <c r="F130" t="n">
-        <v>517784.217026</v>
+        <v>517795.313584</v>
       </c>
       <c r="G130" t="n">
-        <v>653976.1653089999</v>
+        <v>654004.055634</v>
       </c>
       <c r="H130" t="n">
-        <v>846605.77457</v>
+        <v>846677.281814</v>
       </c>
       <c r="I130" t="n">
-        <v>1083511.599619</v>
+        <v>1083738.718938</v>
       </c>
       <c r="J130" t="n">
         <v>2419749.278752</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100381.989876</v>
+        <v>100381.685849</v>
       </c>
       <c r="F131" t="n">
-        <v>131301.695738</v>
+        <v>131300.714682</v>
       </c>
       <c r="G131" t="n">
-        <v>170694.094346</v>
+        <v>170691.356453</v>
       </c>
       <c r="H131" t="n">
-        <v>221445.764561</v>
+        <v>221437.962174</v>
       </c>
       <c r="I131" t="n">
-        <v>282231.576044</v>
+        <v>282204.746778</v>
       </c>
       <c r="J131" t="n">
         <v>212356.680249</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>989015.1691610001</v>
+        <v>989015.659491</v>
       </c>
       <c r="F132" t="n">
-        <v>1047846.595621</v>
+        <v>1047847.618312</v>
       </c>
       <c r="G132" t="n">
-        <v>1184902.411228</v>
+        <v>1184902.891941</v>
       </c>
       <c r="H132" t="n">
-        <v>1370709.870969</v>
+        <v>1370705.742814</v>
       </c>
       <c r="I132" t="n">
-        <v>1588868.981074</v>
+        <v>1588844.316613</v>
       </c>
       <c r="J132" t="n">
         <v>1666479.399555</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>242270.60571</v>
+        <v>242270.307092</v>
       </c>
       <c r="F133" t="n">
-        <v>365742.175806</v>
+        <v>365741.482594</v>
       </c>
       <c r="G133" t="n">
-        <v>574955.857681</v>
+        <v>574954.438025</v>
       </c>
       <c r="H133" t="n">
-        <v>850272.101367</v>
+        <v>850267.804495</v>
       </c>
       <c r="I133" t="n">
-        <v>1169629.515457</v>
+        <v>1169610.883444</v>
       </c>
       <c r="J133" t="n">
         <v>1384784.574543</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>226350.788134</v>
+        <v>226351.295989</v>
       </c>
       <c r="F134" t="n">
-        <v>226876.070253</v>
+        <v>226877.099226</v>
       </c>
       <c r="G134" t="n">
-        <v>253867.701014</v>
+        <v>253869.361614</v>
       </c>
       <c r="H134" t="n">
-        <v>301102.743394</v>
+        <v>301105.288306</v>
       </c>
       <c r="I134" t="n">
-        <v>364598.762539</v>
+        <v>364603.377648</v>
       </c>
       <c r="J134" t="n">
         <v>449067.529504</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>66990.231595</v>
+        <v>66989.962955</v>
       </c>
       <c r="F135" t="n">
-        <v>91128.060677</v>
+        <v>91127.15880200001</v>
       </c>
       <c r="G135" t="n">
-        <v>133372.070495</v>
+        <v>133369.383081</v>
       </c>
       <c r="H135" t="n">
-        <v>189887.489013</v>
+        <v>189879.443735</v>
       </c>
       <c r="I135" t="n">
-        <v>258814.747855</v>
+        <v>258786.006649</v>
       </c>
       <c r="J135" t="n">
         <v>186236.951497</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>240661.440823</v>
+        <v>240661.370931</v>
       </c>
       <c r="F136" t="n">
-        <v>241528.569374</v>
+        <v>241528.132292</v>
       </c>
       <c r="G136" t="n">
-        <v>251847.374509</v>
+        <v>251845.611382</v>
       </c>
       <c r="H136" t="n">
-        <v>269892.998462</v>
+        <v>269887.278732</v>
       </c>
       <c r="I136" t="n">
-        <v>299806.717735</v>
+        <v>299786.627284</v>
       </c>
       <c r="J136" t="n">
         <v>248878.191271</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>65709.961967</v>
+        <v>65710.10834599999</v>
       </c>
       <c r="F137" t="n">
-        <v>72226.367658</v>
+        <v>72226.788556</v>
       </c>
       <c r="G137" t="n">
-        <v>81523.588636</v>
+        <v>81524.425774</v>
       </c>
       <c r="H137" t="n">
-        <v>93723.079706</v>
+        <v>93724.649154</v>
       </c>
       <c r="I137" t="n">
-        <v>109489.170205</v>
+        <v>109493.026573</v>
       </c>
       <c r="J137" t="n">
         <v>142823.130826</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>115459.121842</v>
+        <v>115458.903053</v>
       </c>
       <c r="F138" t="n">
-        <v>123363.474241</v>
+        <v>123362.830024</v>
       </c>
       <c r="G138" t="n">
-        <v>140337.970011</v>
+        <v>140336.235269</v>
       </c>
       <c r="H138" t="n">
-        <v>161175.838024</v>
+        <v>161171.085745</v>
       </c>
       <c r="I138" t="n">
-        <v>183303.429221</v>
+        <v>183287.942505</v>
       </c>
       <c r="J138" t="n">
         <v>130815.688779</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>146245.361858</v>
+        <v>146244.350603</v>
       </c>
       <c r="F139" t="n">
-        <v>165131.890906</v>
+        <v>165128.939675</v>
       </c>
       <c r="G139" t="n">
-        <v>205974.57029</v>
+        <v>205966.881222</v>
       </c>
       <c r="H139" t="n">
-        <v>264716.10497</v>
+        <v>264695.358573</v>
       </c>
       <c r="I139" t="n">
-        <v>336826.199872</v>
+        <v>336757.536653</v>
       </c>
       <c r="J139" t="n">
         <v>76013.468343</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1269690.121318</v>
+        <v>1269686.767128</v>
       </c>
       <c r="F140" t="n">
-        <v>1308003.543462</v>
+        <v>1307993.741012</v>
       </c>
       <c r="G140" t="n">
-        <v>1512140.379886</v>
+        <v>1512114.46075</v>
       </c>
       <c r="H140" t="n">
-        <v>1871484.491878</v>
+        <v>1871412.480373</v>
       </c>
       <c r="I140" t="n">
-        <v>2388640.620425</v>
+        <v>2388392.927539</v>
       </c>
       <c r="J140" t="n">
         <v>1761921.660922</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>70041.057044</v>
+        <v>70041.175693</v>
       </c>
       <c r="F141" t="n">
-        <v>81155.09152</v>
+        <v>81155.44315799999</v>
       </c>
       <c r="G141" t="n">
-        <v>103034.037606</v>
+        <v>103034.862825</v>
       </c>
       <c r="H141" t="n">
-        <v>133505.014975</v>
+        <v>133506.845261</v>
       </c>
       <c r="I141" t="n">
-        <v>171138.172607</v>
+        <v>171143.215748</v>
       </c>
       <c r="J141" t="n">
         <v>234058.860379</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>20305.777578</v>
+        <v>20306.22611</v>
       </c>
       <c r="F142" t="n">
-        <v>37178.570718</v>
+        <v>37181.061084</v>
       </c>
       <c r="G142" t="n">
-        <v>76208.831989</v>
+        <v>76221.08903</v>
       </c>
       <c r="H142" t="n">
-        <v>138233.121111</v>
+        <v>138283.171824</v>
       </c>
       <c r="I142" t="n">
-        <v>217770.830349</v>
+        <v>217980.996626</v>
       </c>
       <c r="J142" t="n">
         <v>1473382.688381</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4255.404744</v>
+        <v>4255.405772</v>
       </c>
       <c r="F146" t="n">
-        <v>4084.360998</v>
+        <v>4084.365186</v>
       </c>
       <c r="G146" t="n">
-        <v>4272.356575</v>
+        <v>4272.369287</v>
       </c>
       <c r="H146" t="n">
-        <v>4864.587538</v>
+        <v>4864.621014</v>
       </c>
       <c r="I146" t="n">
-        <v>5977.682528</v>
+        <v>5977.786059</v>
       </c>
       <c r="J146" t="n">
         <v>6293.908898</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>8330.788108000001</v>
+        <v>8330.775819</v>
       </c>
       <c r="F147" t="n">
-        <v>9250.692128000001</v>
+        <v>9250.656195</v>
       </c>
       <c r="G147" t="n">
-        <v>10928.937711</v>
+        <v>10928.852117</v>
       </c>
       <c r="H147" t="n">
-        <v>13158.746091</v>
+        <v>13158.540743</v>
       </c>
       <c r="I147" t="n">
-        <v>16373.943589</v>
+        <v>16373.301528</v>
       </c>
       <c r="J147" t="n">
         <v>26793.090879</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>468685.640948</v>
+        <v>468685.652209</v>
       </c>
       <c r="F148" t="n">
-        <v>537702.801024</v>
+        <v>537702.832769</v>
       </c>
       <c r="G148" t="n">
-        <v>675041.637755</v>
+        <v>675041.710636</v>
       </c>
       <c r="H148" t="n">
-        <v>856292.517841</v>
+        <v>856292.689713</v>
       </c>
       <c r="I148" t="n">
-        <v>1097368.697853</v>
+        <v>1097369.236382</v>
       </c>
       <c r="J148" t="n">
         <v>1342450.414194</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>31435.405529</v>
+        <v>31435.37988</v>
       </c>
       <c r="F149" t="n">
-        <v>37020.94064</v>
+        <v>37020.870413</v>
       </c>
       <c r="G149" t="n">
-        <v>47144.098913</v>
+        <v>47143.920287</v>
       </c>
       <c r="H149" t="n">
-        <v>60798.021207</v>
+        <v>60797.529475</v>
       </c>
       <c r="I149" t="n">
-        <v>77752.03040800001</v>
+        <v>77750.3073</v>
       </c>
       <c r="J149" t="n">
         <v>137477.501969</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>262324.558012</v>
+        <v>262324.542369</v>
       </c>
       <c r="F150" t="n">
-        <v>305010.383572</v>
+        <v>305010.373496</v>
       </c>
       <c r="G150" t="n">
-        <v>379895.825837</v>
+        <v>379895.781944</v>
       </c>
       <c r="H150" t="n">
-        <v>461207.367003</v>
+        <v>461207.049019</v>
       </c>
       <c r="I150" t="n">
-        <v>547391.7579570001</v>
+        <v>547389.919243</v>
       </c>
       <c r="J150" t="n">
         <v>696815.843485</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>90268.563607</v>
+        <v>90268.50921800001</v>
       </c>
       <c r="F151" t="n">
-        <v>109204.899847</v>
+        <v>109204.744146</v>
       </c>
       <c r="G151" t="n">
-        <v>141763.91664</v>
+        <v>141763.494959</v>
       </c>
       <c r="H151" t="n">
-        <v>178907.972675</v>
+        <v>178906.803008</v>
       </c>
       <c r="I151" t="n">
-        <v>216184.138763</v>
+        <v>216180.24024</v>
       </c>
       <c r="J151" t="n">
         <v>335124.273041</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>167410.265711</v>
+        <v>167409.939642</v>
       </c>
       <c r="F152" t="n">
-        <v>212229.56302</v>
+        <v>212228.510502</v>
       </c>
       <c r="G152" t="n">
-        <v>270608.074106</v>
+        <v>270605.330312</v>
       </c>
       <c r="H152" t="n">
-        <v>326991.658238</v>
+        <v>326984.846423</v>
       </c>
       <c r="I152" t="n">
-        <v>376991.084102</v>
+        <v>376970.947679</v>
       </c>
       <c r="J152" t="n">
         <v>801979.379819</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>193880.308983</v>
+        <v>193880.741029</v>
       </c>
       <c r="F153" t="n">
-        <v>229666.208439</v>
+        <v>229667.528952</v>
       </c>
       <c r="G153" t="n">
-        <v>301905.632162</v>
+        <v>301909.115</v>
       </c>
       <c r="H153" t="n">
-        <v>399256.445981</v>
+        <v>399265.520619</v>
       </c>
       <c r="I153" t="n">
-        <v>514689.64064</v>
+        <v>514718.215991</v>
       </c>
       <c r="J153" t="n">
         <v>91297.960919</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>47756.158157</v>
+        <v>47756.147862</v>
       </c>
       <c r="F154" t="n">
-        <v>59514.938882</v>
+        <v>59514.90689</v>
       </c>
       <c r="G154" t="n">
-        <v>75915.679922</v>
+        <v>75915.585078</v>
       </c>
       <c r="H154" t="n">
-        <v>92054.35327599999</v>
+        <v>92054.069836</v>
       </c>
       <c r="I154" t="n">
-        <v>105753.08451</v>
+        <v>105752.105927</v>
       </c>
       <c r="J154" t="n">
         <v>138934.907147</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>64676.00524</v>
+        <v>64676.000767</v>
       </c>
       <c r="F155" t="n">
-        <v>104429.694629</v>
+        <v>104429.679212</v>
       </c>
       <c r="G155" t="n">
-        <v>164444.991295</v>
+        <v>164444.953176</v>
       </c>
       <c r="H155" t="n">
-        <v>244600.377244</v>
+        <v>244600.297164</v>
       </c>
       <c r="I155" t="n">
-        <v>334083.986846</v>
+        <v>334083.840419</v>
       </c>
       <c r="J155" t="n">
-        <v>440869.53301</v>
+        <v>440869.281834</v>
       </c>
       <c r="K155" t="n">
-        <v>567064.37266</v>
+        <v>567063.960097</v>
       </c>
       <c r="L155" t="n">
-        <v>713486.090778</v>
+        <v>713485.436569</v>
       </c>
       <c r="M155" t="n">
-        <v>874790.863457</v>
+        <v>874789.8616459999</v>
       </c>
       <c r="N155" t="n">
-        <v>1059861.496828</v>
+        <v>1059859.990436</v>
       </c>
       <c r="O155" t="n">
-        <v>1249065.097365</v>
+        <v>1249062.902785</v>
       </c>
       <c r="P155" t="n">
-        <v>1450077.274081</v>
+        <v>1450074.130149</v>
       </c>
       <c r="Q155" t="n">
-        <v>1665603.220904</v>
+        <v>1665598.756296</v>
       </c>
       <c r="R155" t="n">
-        <v>1894632.883636</v>
+        <v>1894626.562249</v>
       </c>
       <c r="S155" t="n">
-        <v>2140590.235458</v>
+        <v>2140581.24654</v>
       </c>
       <c r="T155" t="n">
-        <v>2401303.78119</v>
+        <v>2401290.868743</v>
       </c>
       <c r="U155" t="n">
-        <v>2674536.349368</v>
+        <v>2674517.449776</v>
       </c>
       <c r="V155" t="n">
-        <v>2954644.107341</v>
+        <v>2954615.565303</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>224917.741902</v>
+        <v>224917.736978</v>
       </c>
       <c r="F156" t="n">
-        <v>338623.398353</v>
+        <v>338623.385046</v>
       </c>
       <c r="G156" t="n">
-        <v>489772.916875</v>
+        <v>489772.891726</v>
       </c>
       <c r="H156" t="n">
-        <v>658344.655806</v>
+        <v>658344.61488</v>
       </c>
       <c r="I156" t="n">
-        <v>809859.651109</v>
+        <v>809859.592777</v>
       </c>
       <c r="J156" t="n">
-        <v>962113.263858</v>
+        <v>962113.188824</v>
       </c>
       <c r="K156" t="n">
-        <v>1110497.409532</v>
+        <v>1110497.320694</v>
       </c>
       <c r="L156" t="n">
-        <v>1251788.358232</v>
+        <v>1251788.264135</v>
       </c>
       <c r="M156" t="n">
-        <v>1377301.244252</v>
+        <v>1377301.160896</v>
       </c>
       <c r="N156" t="n">
-        <v>1499495.008349</v>
+        <v>1499494.961562</v>
       </c>
       <c r="O156" t="n">
-        <v>1587979.795955</v>
+        <v>1587979.823343</v>
       </c>
       <c r="P156" t="n">
-        <v>1655560.852712</v>
+        <v>1655561.009356</v>
       </c>
       <c r="Q156" t="n">
-        <v>1706735.996528</v>
+        <v>1706736.36682</v>
       </c>
       <c r="R156" t="n">
-        <v>1743024.630569</v>
+        <v>1743025.326801</v>
       </c>
       <c r="S156" t="n">
-        <v>1768806.708736</v>
+        <v>1768807.886121</v>
       </c>
       <c r="T156" t="n">
-        <v>1785140.388862</v>
+        <v>1785142.268366</v>
       </c>
       <c r="U156" t="n">
-        <v>1793794.343219</v>
+        <v>1793797.280341</v>
       </c>
       <c r="V156" t="n">
-        <v>1794814.097459</v>
+        <v>1794818.696164</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1421.787524</v>
+        <v>1421.788208</v>
       </c>
       <c r="F157" t="n">
-        <v>2699.371328</v>
+        <v>2699.374882</v>
       </c>
       <c r="G157" t="n">
-        <v>4759.826458</v>
+        <v>4759.838505</v>
       </c>
       <c r="H157" t="n">
-        <v>7171.990306</v>
+        <v>7172.018932</v>
       </c>
       <c r="I157" t="n">
-        <v>9236.262777</v>
+        <v>9236.314333</v>
       </c>
       <c r="J157" t="n">
-        <v>10995.997582</v>
+        <v>10996.077918</v>
       </c>
       <c r="K157" t="n">
-        <v>12647.101906</v>
+        <v>12647.219805</v>
       </c>
       <c r="L157" t="n">
-        <v>14335.168394</v>
+        <v>14335.337887</v>
       </c>
       <c r="M157" t="n">
-        <v>16021.612267</v>
+        <v>16021.85245</v>
       </c>
       <c r="N157" t="n">
-        <v>17745.584487</v>
+        <v>17745.920563</v>
       </c>
       <c r="O157" t="n">
-        <v>19052.513736</v>
+        <v>19052.967865</v>
       </c>
       <c r="P157" t="n">
-        <v>20024.888774</v>
+        <v>20025.488106</v>
       </c>
       <c r="Q157" t="n">
-        <v>20646.641495</v>
+        <v>20647.41765</v>
       </c>
       <c r="R157" t="n">
-        <v>20943.605749</v>
+        <v>20944.598403</v>
       </c>
       <c r="S157" t="n">
-        <v>21013.423517</v>
+        <v>21014.689492</v>
       </c>
       <c r="T157" t="n">
-        <v>20910.174245</v>
+        <v>20911.798518</v>
       </c>
       <c r="U157" t="n">
-        <v>20650.087151</v>
+        <v>20652.203003</v>
       </c>
       <c r="V157" t="n">
-        <v>20245.964616</v>
+        <v>20248.802267</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>50136.518086</v>
+        <v>50136.525626</v>
       </c>
       <c r="F158" t="n">
-        <v>66858.228661</v>
+        <v>66858.249631</v>
       </c>
       <c r="G158" t="n">
-        <v>85015.58708100001</v>
+        <v>85015.62691200001</v>
       </c>
       <c r="H158" t="n">
-        <v>104126.341596</v>
+        <v>104126.40804</v>
       </c>
       <c r="I158" t="n">
-        <v>120979.310574</v>
+        <v>120979.413123</v>
       </c>
       <c r="J158" t="n">
-        <v>138971.53168</v>
+        <v>138971.687975</v>
       </c>
       <c r="K158" t="n">
-        <v>157777.890602</v>
+        <v>157778.12585</v>
       </c>
       <c r="L158" t="n">
-        <v>176375.372235</v>
+        <v>176375.71899</v>
       </c>
       <c r="M158" t="n">
-        <v>192497.975997</v>
+        <v>192498.468906</v>
       </c>
       <c r="N158" t="n">
-        <v>207523.596886</v>
+        <v>207524.280981</v>
       </c>
       <c r="O158" t="n">
-        <v>217689.947275</v>
+        <v>217690.863624</v>
       </c>
       <c r="P158" t="n">
-        <v>224551.538184</v>
+        <v>224552.738147</v>
       </c>
       <c r="Q158" t="n">
-        <v>228265.305135</v>
+        <v>228266.849837</v>
       </c>
       <c r="R158" t="n">
-        <v>230559.92092</v>
+        <v>230561.911799</v>
       </c>
       <c r="S158" t="n">
-        <v>232963.755595</v>
+        <v>232966.360242</v>
       </c>
       <c r="T158" t="n">
-        <v>235599.018485</v>
+        <v>235602.496163</v>
       </c>
       <c r="U158" t="n">
-        <v>237657.332072</v>
+        <v>237662.078213</v>
       </c>
       <c r="V158" t="n">
-        <v>238226.840294</v>
+        <v>238233.499859</v>
       </c>
     </row>
     <row r="159">
@@ -12458,58 +12458,58 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>605.950662</v>
+        <v>605.950861</v>
       </c>
       <c r="F159" t="n">
-        <v>877.565694</v>
+        <v>877.566325</v>
       </c>
       <c r="G159" t="n">
-        <v>1242.743547</v>
+        <v>1242.744996</v>
       </c>
       <c r="H159" t="n">
-        <v>1643.778236</v>
+        <v>1643.78099</v>
       </c>
       <c r="I159" t="n">
-        <v>2010.099665</v>
+        <v>2010.104256</v>
       </c>
       <c r="J159" t="n">
-        <v>2380.162822</v>
+        <v>2380.17003</v>
       </c>
       <c r="K159" t="n">
-        <v>2785.940514</v>
+        <v>2785.951625</v>
       </c>
       <c r="L159" t="n">
-        <v>3202.4404</v>
+        <v>3202.457054</v>
       </c>
       <c r="M159" t="n">
-        <v>3568.813539</v>
+        <v>3568.837358</v>
       </c>
       <c r="N159" t="n">
-        <v>3897.736209</v>
+        <v>3897.769132</v>
       </c>
       <c r="O159" t="n">
-        <v>4134.680277</v>
+        <v>4134.724309</v>
       </c>
       <c r="P159" t="n">
-        <v>4319.663142</v>
+        <v>4319.721216</v>
       </c>
       <c r="Q159" t="n">
-        <v>4436.939201</v>
+        <v>4437.014614</v>
       </c>
       <c r="R159" t="n">
-        <v>4462.295141</v>
+        <v>4462.391017</v>
       </c>
       <c r="S159" t="n">
-        <v>4405.321257</v>
+        <v>4405.441225</v>
       </c>
       <c r="T159" t="n">
-        <v>4283.621827</v>
+        <v>4283.771333</v>
       </c>
       <c r="U159" t="n">
-        <v>4127.293648</v>
+        <v>4127.482453</v>
       </c>
       <c r="V159" t="n">
-        <v>3962.147913</v>
+        <v>3962.394599</v>
       </c>
     </row>
     <row r="160">
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>13133.151586</v>
+        <v>13133.15256</v>
       </c>
       <c r="F160" t="n">
-        <v>20557.400556</v>
+        <v>20557.404125</v>
       </c>
       <c r="G160" t="n">
-        <v>32192.706904</v>
+        <v>32192.716846</v>
       </c>
       <c r="H160" t="n">
-        <v>47646.440972</v>
+        <v>47646.464154</v>
       </c>
       <c r="I160" t="n">
-        <v>64497.103189</v>
+        <v>64497.149251</v>
       </c>
       <c r="J160" t="n">
-        <v>83085.425208</v>
+        <v>83085.507579</v>
       </c>
       <c r="K160" t="n">
-        <v>103363.344946</v>
+        <v>103363.48209</v>
       </c>
       <c r="L160" t="n">
-        <v>124716.030961</v>
+        <v>124716.246365</v>
       </c>
       <c r="M160" t="n">
-        <v>147136.094488</v>
+        <v>147136.422744</v>
       </c>
       <c r="N160" t="n">
-        <v>172978.227241</v>
+        <v>172978.727327</v>
       </c>
       <c r="O160" t="n">
-        <v>199665.446391</v>
+        <v>199666.199075</v>
       </c>
       <c r="P160" t="n">
-        <v>228607.029507</v>
+        <v>228608.159426</v>
       </c>
       <c r="Q160" t="n">
-        <v>260161.124738</v>
+        <v>260162.822783</v>
       </c>
       <c r="R160" t="n">
-        <v>293777.495285</v>
+        <v>293780.041031</v>
       </c>
       <c r="S160" t="n">
-        <v>329767.389306</v>
+        <v>329771.210249</v>
       </c>
       <c r="T160" t="n">
-        <v>368478.263511</v>
+        <v>368484.044998</v>
       </c>
       <c r="U160" t="n">
-        <v>410269.629803</v>
+        <v>410278.541475</v>
       </c>
       <c r="V160" t="n">
-        <v>455381.421476</v>
+        <v>455395.620908</v>
       </c>
     </row>
     <row r="161">
@@ -12686,58 +12686,58 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14851.065916</v>
+        <v>14851.079155</v>
       </c>
       <c r="F162" t="n">
-        <v>12393.259815</v>
+        <v>12393.277502</v>
       </c>
       <c r="G162" t="n">
-        <v>10358.530923</v>
+        <v>10358.548125</v>
       </c>
       <c r="H162" t="n">
-        <v>9823.788542</v>
+        <v>9823.806117</v>
       </c>
       <c r="I162" t="n">
-        <v>10124.430546</v>
+        <v>10124.450218</v>
       </c>
       <c r="J162" t="n">
-        <v>11163.309269</v>
+        <v>11163.333824</v>
       </c>
       <c r="K162" t="n">
-        <v>12672.510998</v>
+        <v>12672.544062</v>
       </c>
       <c r="L162" t="n">
-        <v>14571.205992</v>
+        <v>14571.252943</v>
       </c>
       <c r="M162" t="n">
-        <v>16886.794262</v>
+        <v>16886.863492</v>
       </c>
       <c r="N162" t="n">
-        <v>19557.423435</v>
+        <v>19557.526614</v>
       </c>
       <c r="O162" t="n">
-        <v>22202.057739</v>
+        <v>22202.206991</v>
       </c>
       <c r="P162" t="n">
-        <v>24416.300822</v>
+        <v>24416.505589</v>
       </c>
       <c r="Q162" t="n">
-        <v>26106.351377</v>
+        <v>26106.619157</v>
       </c>
       <c r="R162" t="n">
-        <v>27396.783198</v>
+        <v>27397.12395</v>
       </c>
       <c r="S162" t="n">
-        <v>28423.827941</v>
+        <v>28424.257834</v>
       </c>
       <c r="T162" t="n">
-        <v>29234.017578</v>
+        <v>29234.563202</v>
       </c>
       <c r="U162" t="n">
-        <v>29835.7899</v>
+        <v>29836.494706</v>
       </c>
       <c r="V162" t="n">
-        <v>30257.663693</v>
+        <v>30258.602576</v>
       </c>
     </row>
     <row r="163">
@@ -12762,58 +12762,58 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1475.173309</v>
+        <v>1475.175509</v>
       </c>
       <c r="F163" t="n">
-        <v>2004.278469</v>
+        <v>2004.285706</v>
       </c>
       <c r="G163" t="n">
-        <v>2689.851631</v>
+        <v>2689.869289</v>
       </c>
       <c r="H163" t="n">
-        <v>3460.474997</v>
+        <v>3460.509988</v>
       </c>
       <c r="I163" t="n">
-        <v>4168.322806</v>
+        <v>4168.381641</v>
       </c>
       <c r="J163" t="n">
-        <v>4824.748876</v>
+        <v>4824.838373</v>
       </c>
       <c r="K163" t="n">
-        <v>5403.552449</v>
+        <v>5403.679716</v>
       </c>
       <c r="L163" t="n">
-        <v>5952.554186</v>
+        <v>5952.728966</v>
       </c>
       <c r="M163" t="n">
-        <v>6548.164792</v>
+        <v>6548.402566</v>
       </c>
       <c r="N163" t="n">
-        <v>7177.004514</v>
+        <v>7177.324995</v>
       </c>
       <c r="O163" t="n">
-        <v>7772.481518</v>
+        <v>7772.906554</v>
       </c>
       <c r="P163" t="n">
-        <v>8271.642320999999</v>
+        <v>8272.195315000001</v>
       </c>
       <c r="Q163" t="n">
-        <v>8683.783799000001</v>
+        <v>8684.494360000001</v>
       </c>
       <c r="R163" t="n">
-        <v>9071.475990999999</v>
+        <v>9072.390732</v>
       </c>
       <c r="S163" t="n">
-        <v>9485.575977</v>
+        <v>9486.769993</v>
       </c>
       <c r="T163" t="n">
-        <v>9921.922213</v>
+        <v>9923.510783</v>
       </c>
       <c r="U163" t="n">
-        <v>10353.21819</v>
+        <v>10355.38122</v>
       </c>
       <c r="V163" t="n">
-        <v>10767.865905</v>
+        <v>10770.910916</v>
       </c>
     </row>
     <row r="164">
@@ -12838,58 +12838,58 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>16371.228746</v>
+        <v>16371.23568</v>
       </c>
       <c r="F164" t="n">
-        <v>24303.547554</v>
+        <v>24303.577639</v>
       </c>
       <c r="G164" t="n">
-        <v>34678.563443</v>
+        <v>34678.651499</v>
       </c>
       <c r="H164" t="n">
-        <v>47800.366071</v>
+        <v>47800.568653</v>
       </c>
       <c r="I164" t="n">
-        <v>61907.902509</v>
+        <v>61908.290757</v>
       </c>
       <c r="J164" t="n">
-        <v>76782.97584</v>
+        <v>76783.636076</v>
       </c>
       <c r="K164" t="n">
-        <v>91005.480998</v>
+        <v>91006.502456</v>
       </c>
       <c r="L164" t="n">
-        <v>103132.738246</v>
+        <v>103134.191323</v>
       </c>
       <c r="M164" t="n">
-        <v>114501.419417</v>
+        <v>114503.406373</v>
       </c>
       <c r="N164" t="n">
-        <v>125545.11348</v>
+        <v>125547.771708</v>
       </c>
       <c r="O164" t="n">
-        <v>136206.217044</v>
+        <v>136209.735856</v>
       </c>
       <c r="P164" t="n">
-        <v>145748.972426</v>
+        <v>145753.581768</v>
       </c>
       <c r="Q164" t="n">
-        <v>154381.424584</v>
+        <v>154387.433375</v>
       </c>
       <c r="R164" t="n">
-        <v>162371.382979</v>
+        <v>162379.215566</v>
       </c>
       <c r="S164" t="n">
-        <v>170017.03606</v>
+        <v>170027.305165</v>
       </c>
       <c r="T164" t="n">
-        <v>177382.942953</v>
+        <v>177396.585679</v>
       </c>
       <c r="U164" t="n">
-        <v>184625.416912</v>
+        <v>184643.969943</v>
       </c>
       <c r="V164" t="n">
-        <v>191940.294737</v>
+        <v>191966.469673</v>
       </c>
     </row>
     <row r="165">
@@ -12914,58 +12914,58 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>57649.828703</v>
+        <v>57649.786262</v>
       </c>
       <c r="F165" t="n">
-        <v>76179.334819</v>
+        <v>76179.21756600001</v>
       </c>
       <c r="G165" t="n">
-        <v>87536.88772</v>
+        <v>87536.671906</v>
       </c>
       <c r="H165" t="n">
-        <v>102347.642852</v>
+        <v>102347.280003</v>
       </c>
       <c r="I165" t="n">
-        <v>119590.583748</v>
+        <v>119590.008792</v>
       </c>
       <c r="J165" t="n">
-        <v>140860.283472</v>
+        <v>140859.39687</v>
       </c>
       <c r="K165" t="n">
-        <v>164321.555003</v>
+        <v>164320.232214</v>
       </c>
       <c r="L165" t="n">
-        <v>190724.733423</v>
+        <v>190722.807403</v>
       </c>
       <c r="M165" t="n">
-        <v>221694.954631</v>
+        <v>221692.190029</v>
       </c>
       <c r="N165" t="n">
-        <v>257944.698803</v>
+        <v>257940.767813</v>
       </c>
       <c r="O165" t="n">
-        <v>298213.77852</v>
+        <v>298208.251022</v>
       </c>
       <c r="P165" t="n">
-        <v>340992.420917</v>
+        <v>340984.739398</v>
       </c>
       <c r="Q165" t="n">
-        <v>386974.827099</v>
+        <v>386964.199431</v>
       </c>
       <c r="R165" t="n">
-        <v>436754.139637</v>
+        <v>436739.411471</v>
       </c>
       <c r="S165" t="n">
-        <v>491024.383257</v>
+        <v>491003.829878</v>
       </c>
       <c r="T165" t="n">
-        <v>549904.315983</v>
+        <v>549875.2842540001</v>
       </c>
       <c r="U165" t="n">
-        <v>613109.518841</v>
+        <v>613067.702856</v>
       </c>
       <c r="V165" t="n">
-        <v>681848.936626</v>
+        <v>681786.573726</v>
       </c>
     </row>
     <row r="166">
@@ -12990,58 +12990,58 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>57204.078609</v>
+        <v>57204.061383</v>
       </c>
       <c r="F166" t="n">
-        <v>70458.92645699999</v>
+        <v>70458.88583499999</v>
       </c>
       <c r="G166" t="n">
-        <v>83080.564327</v>
+        <v>83080.494832</v>
       </c>
       <c r="H166" t="n">
-        <v>98723.65349500001</v>
+        <v>98723.542466</v>
       </c>
       <c r="I166" t="n">
-        <v>114106.998219</v>
+        <v>114106.829853</v>
       </c>
       <c r="J166" t="n">
-        <v>130582.897248</v>
+        <v>130582.64798</v>
       </c>
       <c r="K166" t="n">
-        <v>145815.505683</v>
+        <v>145815.149732</v>
       </c>
       <c r="L166" t="n">
-        <v>159913.982001</v>
+        <v>159913.491403</v>
       </c>
       <c r="M166" t="n">
-        <v>173389.795374</v>
+        <v>173389.13789</v>
       </c>
       <c r="N166" t="n">
-        <v>186344.072385</v>
+        <v>186343.208517</v>
       </c>
       <c r="O166" t="n">
-        <v>197650.659186</v>
+        <v>197649.544294</v>
       </c>
       <c r="P166" t="n">
-        <v>206107.859573</v>
+        <v>206106.443004</v>
       </c>
       <c r="Q166" t="n">
-        <v>212211.131992</v>
+        <v>212209.343597</v>
       </c>
       <c r="R166" t="n">
-        <v>216721.041376</v>
+        <v>216718.779175</v>
       </c>
       <c r="S166" t="n">
-        <v>220562.069283</v>
+        <v>220559.182494</v>
       </c>
       <c r="T166" t="n">
-        <v>223732.837275</v>
+        <v>223729.107184</v>
       </c>
       <c r="U166" t="n">
-        <v>226342.584873</v>
+        <v>226337.664629</v>
       </c>
       <c r="V166" t="n">
-        <v>228838.009719</v>
+        <v>228831.280932</v>
       </c>
     </row>
     <row r="167">
@@ -13066,58 +13066,58 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>530833.9067620001</v>
+        <v>530833.789038</v>
       </c>
       <c r="F167" t="n">
-        <v>626530.993268</v>
+        <v>626530.703809</v>
       </c>
       <c r="G167" t="n">
-        <v>724841.455461</v>
+        <v>724840.932719</v>
       </c>
       <c r="H167" t="n">
-        <v>876417.809992</v>
+        <v>876416.929143</v>
       </c>
       <c r="I167" t="n">
-        <v>1060968.19538</v>
+        <v>1060966.791758</v>
       </c>
       <c r="J167" t="n">
-        <v>1283367.069705</v>
+        <v>1283364.894894</v>
       </c>
       <c r="K167" t="n">
-        <v>1519259.93685</v>
+        <v>1519256.68307</v>
       </c>
       <c r="L167" t="n">
-        <v>1762241.470218</v>
+        <v>1762236.771921</v>
       </c>
       <c r="M167" t="n">
-        <v>2018077.880643</v>
+        <v>2018071.280642</v>
       </c>
       <c r="N167" t="n">
-        <v>2288389.429291</v>
+        <v>2288380.339247</v>
       </c>
       <c r="O167" t="n">
-        <v>2553629.505547</v>
+        <v>2553617.227455</v>
       </c>
       <c r="P167" t="n">
-        <v>2795154.499435</v>
+        <v>2795138.237005</v>
       </c>
       <c r="Q167" t="n">
-        <v>3013039.660231</v>
+        <v>3013018.369316</v>
       </c>
       <c r="R167" t="n">
-        <v>3209852.069571</v>
+        <v>3209824.275939</v>
       </c>
       <c r="S167" t="n">
-        <v>3387309.768401</v>
+        <v>3387273.346419</v>
       </c>
       <c r="T167" t="n">
-        <v>3537340.893033</v>
+        <v>3537292.771174</v>
       </c>
       <c r="U167" t="n">
-        <v>3653409.285773</v>
+        <v>3653344.648241</v>
       </c>
       <c r="V167" t="n">
-        <v>3741747.18667</v>
+        <v>3741657.482168</v>
       </c>
     </row>
     <row r="168">
@@ -13142,58 +13142,58 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>450.053754</v>
+        <v>450.054881</v>
       </c>
       <c r="F168" t="n">
-        <v>581.766019</v>
+        <v>581.769306</v>
       </c>
       <c r="G168" t="n">
-        <v>720.394504</v>
+        <v>720.401315</v>
       </c>
       <c r="H168" t="n">
-        <v>898.443562</v>
+        <v>898.456023</v>
       </c>
       <c r="I168" t="n">
-        <v>1093.877818</v>
+        <v>1093.898505</v>
       </c>
       <c r="J168" t="n">
-        <v>1320.251342</v>
+        <v>1320.283967</v>
       </c>
       <c r="K168" t="n">
-        <v>1559.603648</v>
+        <v>1559.652628</v>
       </c>
       <c r="L168" t="n">
-        <v>1810.052215</v>
+        <v>1810.123137</v>
       </c>
       <c r="M168" t="n">
-        <v>2078.165552</v>
+        <v>2078.265889</v>
       </c>
       <c r="N168" t="n">
-        <v>2364.860547</v>
+        <v>2365.000176</v>
       </c>
       <c r="O168" t="n">
-        <v>2646.209112</v>
+        <v>2646.399569</v>
       </c>
       <c r="P168" t="n">
-        <v>2897.535703</v>
+        <v>2897.789789</v>
       </c>
       <c r="Q168" t="n">
-        <v>3116.682268</v>
+        <v>3117.0159</v>
       </c>
       <c r="R168" t="n">
-        <v>3308.364767</v>
+        <v>3308.799368</v>
       </c>
       <c r="S168" t="n">
-        <v>3478.154507</v>
+        <v>3478.720703</v>
       </c>
       <c r="T168" t="n">
-        <v>3622.782308</v>
+        <v>3623.52478</v>
       </c>
       <c r="U168" t="n">
-        <v>3739.682627</v>
+        <v>3740.67118</v>
       </c>
       <c r="V168" t="n">
-        <v>3835.079995</v>
+        <v>3836.43691</v>
       </c>
     </row>
     <row r="169">
@@ -13218,58 +13218,58 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>291412.884099</v>
+        <v>291412.814505</v>
       </c>
       <c r="F169" t="n">
-        <v>368978.56683</v>
+        <v>368978.392864</v>
       </c>
       <c r="G169" t="n">
-        <v>449007.987139</v>
+        <v>449007.664359</v>
       </c>
       <c r="H169" t="n">
-        <v>572082.739177</v>
+        <v>572082.179274</v>
       </c>
       <c r="I169" t="n">
-        <v>733643.321779</v>
+        <v>733642.4115320001</v>
       </c>
       <c r="J169" t="n">
-        <v>946303.43918</v>
+        <v>946302.008291</v>
       </c>
       <c r="K169" t="n">
-        <v>1201450.943286</v>
+        <v>1201448.773216</v>
       </c>
       <c r="L169" t="n">
-        <v>1492589.641477</v>
+        <v>1492586.443187</v>
       </c>
       <c r="M169" t="n">
-        <v>1833459.103469</v>
+        <v>1833454.52977</v>
       </c>
       <c r="N169" t="n">
-        <v>2243322.998099</v>
+        <v>2243316.659053</v>
       </c>
       <c r="O169" t="n">
-        <v>2721162.714831</v>
+        <v>2721154.235058</v>
       </c>
       <c r="P169" t="n">
-        <v>3249894.728511</v>
+        <v>3249883.752606</v>
       </c>
       <c r="Q169" t="n">
-        <v>3831207.493529</v>
+        <v>3831193.617235</v>
       </c>
       <c r="R169" t="n">
-        <v>4468742.257574</v>
+        <v>4468724.905657</v>
       </c>
       <c r="S169" t="n">
-        <v>5169421.584933</v>
+        <v>5169400.008991</v>
       </c>
       <c r="T169" t="n">
-        <v>5927954.529951</v>
+        <v>5927927.883017</v>
       </c>
       <c r="U169" t="n">
-        <v>6736697.449185</v>
+        <v>6736664.686272</v>
       </c>
       <c r="V169" t="n">
-        <v>7606556.877572</v>
+        <v>7606516.566472</v>
       </c>
     </row>
     <row r="170">
@@ -13294,58 +13294,58 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>12666.325999</v>
+        <v>12666.33411</v>
       </c>
       <c r="F170" t="n">
-        <v>20152.572177</v>
+        <v>20152.607673</v>
       </c>
       <c r="G170" t="n">
-        <v>29210.136275</v>
+        <v>29210.233363</v>
       </c>
       <c r="H170" t="n">
-        <v>40159.460253</v>
+        <v>40159.666776</v>
       </c>
       <c r="I170" t="n">
-        <v>51812.08841</v>
+        <v>51812.458837</v>
       </c>
       <c r="J170" t="n">
-        <v>64680.519485</v>
+        <v>64681.124167</v>
       </c>
       <c r="K170" t="n">
-        <v>78700.060547</v>
+        <v>78700.99262</v>
       </c>
       <c r="L170" t="n">
-        <v>94589.21171800001</v>
+        <v>94590.609197</v>
       </c>
       <c r="M170" t="n">
-        <v>113268.48616</v>
+        <v>113270.560558</v>
       </c>
       <c r="N170" t="n">
-        <v>135055.067298</v>
+        <v>135058.120325</v>
       </c>
       <c r="O170" t="n">
-        <v>158683.892161</v>
+        <v>158688.305664</v>
       </c>
       <c r="P170" t="n">
-        <v>182783.702418</v>
+        <v>182789.952517</v>
       </c>
       <c r="Q170" t="n">
-        <v>207381.75177</v>
+        <v>207390.479847</v>
       </c>
       <c r="R170" t="n">
-        <v>233339.297391</v>
+        <v>233351.46233</v>
       </c>
       <c r="S170" t="n">
-        <v>261310.660894</v>
+        <v>261327.721463</v>
       </c>
       <c r="T170" t="n">
-        <v>290977.224866</v>
+        <v>291001.416068</v>
       </c>
       <c r="U170" t="n">
-        <v>321926.301136</v>
+        <v>321961.219402</v>
       </c>
       <c r="V170" t="n">
-        <v>354852.455649</v>
+        <v>354904.602616</v>
       </c>
     </row>
     <row r="171">
@@ -13370,58 +13370,58 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>67286.133994</v>
+        <v>67286.210549</v>
       </c>
       <c r="F171" t="n">
-        <v>82671.67623</v>
+        <v>82671.892538</v>
       </c>
       <c r="G171" t="n">
-        <v>97544.24670800001</v>
+        <v>97544.67997500001</v>
       </c>
       <c r="H171" t="n">
-        <v>115928.978286</v>
+        <v>115929.739459</v>
       </c>
       <c r="I171" t="n">
-        <v>134327.581498</v>
+        <v>134328.787979</v>
       </c>
       <c r="J171" t="n">
-        <v>154101.704338</v>
+        <v>154103.514383</v>
       </c>
       <c r="K171" t="n">
-        <v>172883.061233</v>
+        <v>172885.640771</v>
       </c>
       <c r="L171" t="n">
-        <v>190443.74577</v>
+        <v>190447.289118</v>
       </c>
       <c r="M171" t="n">
-        <v>207388.263623</v>
+        <v>207393.017457</v>
       </c>
       <c r="N171" t="n">
-        <v>223830.966318</v>
+        <v>223837.241294</v>
       </c>
       <c r="O171" t="n">
-        <v>238172.928767</v>
+        <v>238181.070068</v>
       </c>
       <c r="P171" t="n">
-        <v>248687.090327</v>
+        <v>248697.448455</v>
       </c>
       <c r="Q171" t="n">
-        <v>255517.521228</v>
+        <v>255530.510277</v>
       </c>
       <c r="R171" t="n">
-        <v>259225.34904</v>
+        <v>259241.51075</v>
       </c>
       <c r="S171" t="n">
-        <v>260539.464143</v>
+        <v>260559.57845</v>
       </c>
       <c r="T171" t="n">
-        <v>259589.071309</v>
+        <v>259614.285872</v>
       </c>
       <c r="U171" t="n">
-        <v>256756.908201</v>
+        <v>256789.060345</v>
       </c>
       <c r="V171" t="n">
-        <v>252974.383396</v>
+        <v>253016.774852</v>
       </c>
     </row>
     <row r="172">
@@ -13446,58 +13446,58 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>178286.399102</v>
+        <v>178286.800456</v>
       </c>
       <c r="F172" t="n">
-        <v>210513.077628</v>
+        <v>210514.114698</v>
       </c>
       <c r="G172" t="n">
-        <v>232485.395259</v>
+        <v>232487.226875</v>
       </c>
       <c r="H172" t="n">
-        <v>262427.585196</v>
+        <v>262430.496838</v>
       </c>
       <c r="I172" t="n">
-        <v>297957.523182</v>
+        <v>297961.913105</v>
       </c>
       <c r="J172" t="n">
-        <v>341417.820488</v>
+        <v>341424.278358</v>
       </c>
       <c r="K172" t="n">
-        <v>387144.193125</v>
+        <v>387153.389227</v>
       </c>
       <c r="L172" t="n">
-        <v>433550.725049</v>
+        <v>433563.45719</v>
       </c>
       <c r="M172" t="n">
-        <v>481992.837392</v>
+        <v>482010.152977</v>
       </c>
       <c r="N172" t="n">
-        <v>532575.314038</v>
+        <v>532598.567159</v>
       </c>
       <c r="O172" t="n">
-        <v>579856.913289</v>
+        <v>579887.627547</v>
       </c>
       <c r="P172" t="n">
-        <v>619518.725843</v>
+        <v>619558.580565</v>
       </c>
       <c r="Q172" t="n">
-        <v>651914.134162</v>
+        <v>651965.254403</v>
       </c>
       <c r="R172" t="n">
-        <v>678609.958673</v>
+        <v>678675.267761</v>
       </c>
       <c r="S172" t="n">
-        <v>700091.0792940001</v>
+        <v>700174.630367</v>
       </c>
       <c r="T172" t="n">
-        <v>714796.533396</v>
+        <v>714903.965322</v>
       </c>
       <c r="U172" t="n">
-        <v>722083.42586</v>
+        <v>722223.355534</v>
       </c>
       <c r="V172" t="n">
-        <v>723115.6883940001</v>
+        <v>723303.155717</v>
       </c>
     </row>
     <row r="173">
@@ -13522,58 +13522,58 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1012.639261</v>
+        <v>1012.639237</v>
       </c>
       <c r="F173" t="n">
-        <v>1531.586625</v>
+        <v>1531.586826</v>
       </c>
       <c r="G173" t="n">
-        <v>2146.30196</v>
+        <v>2146.302907</v>
       </c>
       <c r="H173" t="n">
-        <v>2897.428449</v>
+        <v>2897.430753</v>
       </c>
       <c r="I173" t="n">
-        <v>3747.024536</v>
+        <v>3747.028914</v>
       </c>
       <c r="J173" t="n">
-        <v>4740.228061</v>
+        <v>4740.235393</v>
       </c>
       <c r="K173" t="n">
-        <v>5888.701905</v>
+        <v>5888.713565</v>
       </c>
       <c r="L173" t="n">
-        <v>7258.574482</v>
+        <v>7258.592991</v>
       </c>
       <c r="M173" t="n">
-        <v>8936.640004999999</v>
+        <v>8936.669776000001</v>
       </c>
       <c r="N173" t="n">
-        <v>10968.790246</v>
+        <v>10968.838193</v>
       </c>
       <c r="O173" t="n">
-        <v>13283.883507</v>
+        <v>13283.959389</v>
       </c>
       <c r="P173" t="n">
-        <v>15777.241932</v>
+        <v>15777.359117</v>
       </c>
       <c r="Q173" t="n">
-        <v>18448.768539</v>
+        <v>18448.945881</v>
       </c>
       <c r="R173" t="n">
-        <v>21372.378022</v>
+        <v>21372.64427</v>
       </c>
       <c r="S173" t="n">
-        <v>24605.742672</v>
+        <v>24606.14335</v>
       </c>
       <c r="T173" t="n">
-        <v>28147.868172</v>
+        <v>28148.475863</v>
       </c>
       <c r="U173" t="n">
-        <v>31974.87575</v>
+        <v>31975.811598</v>
       </c>
       <c r="V173" t="n">
-        <v>36189.266457</v>
+        <v>36190.754371</v>
       </c>
     </row>
     <row r="174">
@@ -13598,58 +13598,58 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>619176.955761</v>
+        <v>619176.969465</v>
       </c>
       <c r="F174" t="n">
-        <v>726237.359409</v>
+        <v>726237.428153</v>
       </c>
       <c r="G174" t="n">
-        <v>824106.156466</v>
+        <v>824106.329237</v>
       </c>
       <c r="H174" t="n">
-        <v>967541.901557</v>
+        <v>967542.2506959999</v>
       </c>
       <c r="I174" t="n">
-        <v>1133459.989914</v>
+        <v>1133460.619564</v>
       </c>
       <c r="J174" t="n">
-        <v>1348618.04555</v>
+        <v>1348619.197003</v>
       </c>
       <c r="K174" t="n">
-        <v>1587804.62114</v>
+        <v>1587806.647219</v>
       </c>
       <c r="L174" t="n">
-        <v>1828112.762632</v>
+        <v>1828116.070662</v>
       </c>
       <c r="M174" t="n">
-        <v>2052548.799243</v>
+        <v>2052553.743705</v>
       </c>
       <c r="N174" t="n">
-        <v>2256554.012877</v>
+        <v>2256560.919275</v>
       </c>
       <c r="O174" t="n">
-        <v>2422346.887258</v>
+        <v>2422356.050878</v>
       </c>
       <c r="P174" t="n">
-        <v>2539659.826746</v>
+        <v>2539671.532018</v>
       </c>
       <c r="Q174" t="n">
-        <v>2621452.978843</v>
+        <v>2621467.685477</v>
       </c>
       <c r="R174" t="n">
-        <v>2682883.271041</v>
+        <v>2682901.727152</v>
       </c>
       <c r="S174" t="n">
-        <v>2729414.552747</v>
+        <v>2729437.858402</v>
       </c>
       <c r="T174" t="n">
-        <v>2755825.903679</v>
+        <v>2755855.568868</v>
       </c>
       <c r="U174" t="n">
-        <v>2760736.378765</v>
+        <v>2760774.714772</v>
       </c>
       <c r="V174" t="n">
-        <v>2749710.236519</v>
+        <v>2749761.225448</v>
       </c>
     </row>
     <row r="175">
@@ -13674,58 +13674,58 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2100.934739</v>
+        <v>2100.933702</v>
       </c>
       <c r="F175" t="n">
-        <v>3742.872254</v>
+        <v>3742.868971</v>
       </c>
       <c r="G175" t="n">
-        <v>6166.468557</v>
+        <v>6166.461515</v>
       </c>
       <c r="H175" t="n">
-        <v>9598.872224999999</v>
+        <v>9598.859168000001</v>
       </c>
       <c r="I175" t="n">
-        <v>14041.135014</v>
+        <v>14041.113141</v>
       </c>
       <c r="J175" t="n">
-        <v>19651.073932</v>
+        <v>19651.039053</v>
       </c>
       <c r="K175" t="n">
-        <v>26387.89779</v>
+        <v>26387.844507</v>
       </c>
       <c r="L175" t="n">
-        <v>34337.278237</v>
+        <v>34337.199684</v>
       </c>
       <c r="M175" t="n">
-        <v>43987.35988</v>
+        <v>43987.249036</v>
       </c>
       <c r="N175" t="n">
-        <v>55491.621824</v>
+        <v>55491.47105</v>
       </c>
       <c r="O175" t="n">
-        <v>68663.70909</v>
+        <v>68663.508907</v>
       </c>
       <c r="P175" t="n">
-        <v>83341.639003</v>
+        <v>83341.379785</v>
       </c>
       <c r="Q175" t="n">
-        <v>99761.325897</v>
+        <v>99760.993903</v>
       </c>
       <c r="R175" t="n">
-        <v>118342.753737</v>
+        <v>118342.328013</v>
       </c>
       <c r="S175" t="n">
-        <v>139662.52685</v>
+        <v>139661.982541</v>
       </c>
       <c r="T175" t="n">
-        <v>163909.901662</v>
+        <v>163909.215841</v>
       </c>
       <c r="U175" t="n">
-        <v>190995.532892</v>
+        <v>190994.673967</v>
       </c>
       <c r="V175" t="n">
-        <v>221322.66961</v>
+        <v>221321.577478</v>
       </c>
     </row>
     <row r="176">
@@ -13750,58 +13750,58 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>178.222113</v>
+        <v>178.222844</v>
       </c>
       <c r="F176" t="n">
-        <v>197.464208</v>
+        <v>197.465925</v>
       </c>
       <c r="G176" t="n">
-        <v>221.913267</v>
+        <v>221.916379</v>
       </c>
       <c r="H176" t="n">
-        <v>264.820485</v>
+        <v>264.825858</v>
       </c>
       <c r="I176" t="n">
-        <v>319.68814</v>
+        <v>319.697022</v>
       </c>
       <c r="J176" t="n">
-        <v>385.691519</v>
+        <v>385.705645</v>
       </c>
       <c r="K176" t="n">
-        <v>456.230913</v>
+        <v>456.252361</v>
       </c>
       <c r="L176" t="n">
-        <v>530.328489</v>
+        <v>530.359884</v>
       </c>
       <c r="M176" t="n">
-        <v>611.371476</v>
+        <v>611.416477</v>
       </c>
       <c r="N176" t="n">
-        <v>701.792566</v>
+        <v>701.856316</v>
       </c>
       <c r="O176" t="n">
-        <v>800.369024</v>
+        <v>800.458358</v>
       </c>
       <c r="P176" t="n">
-        <v>905.306054</v>
+        <v>905.430266</v>
       </c>
       <c r="Q176" t="n">
-        <v>1020.606876</v>
+        <v>1020.779696</v>
       </c>
       <c r="R176" t="n">
-        <v>1149.273189</v>
+        <v>1149.514917</v>
       </c>
       <c r="S176" t="n">
-        <v>1293.861842</v>
+        <v>1294.203198</v>
       </c>
       <c r="T176" t="n">
-        <v>1453.007279</v>
+        <v>1453.495238</v>
       </c>
       <c r="U176" t="n">
-        <v>1625.810663</v>
+        <v>1626.521453</v>
       </c>
       <c r="V176" t="n">
-        <v>1815.951065</v>
+        <v>1817.021695</v>
       </c>
     </row>
     <row r="177">
@@ -13826,58 +13826,58 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>572506.263286</v>
+        <v>572505.984816</v>
       </c>
       <c r="F177" t="n">
-        <v>922262.085908</v>
+        <v>922261.285082</v>
       </c>
       <c r="G177" t="n">
-        <v>1336529.309581</v>
+        <v>1336527.762936</v>
       </c>
       <c r="H177" t="n">
-        <v>1786983.761907</v>
+        <v>1786981.155884</v>
       </c>
       <c r="I177" t="n">
-        <v>2188549.809498</v>
+        <v>2188545.740214</v>
       </c>
       <c r="J177" t="n">
-        <v>2559979.55732</v>
+        <v>2559973.398052</v>
       </c>
       <c r="K177" t="n">
-        <v>2883687.266121</v>
+        <v>2883678.294781</v>
       </c>
       <c r="L177" t="n">
-        <v>3218192.35473</v>
+        <v>3218179.775231</v>
       </c>
       <c r="M177" t="n">
-        <v>3591875.006046</v>
+        <v>3591857.869548</v>
       </c>
       <c r="N177" t="n">
-        <v>3993797.267525</v>
+        <v>3993774.408947</v>
       </c>
       <c r="O177" t="n">
-        <v>4381945.945808</v>
+        <v>4381916.079653</v>
       </c>
       <c r="P177" t="n">
-        <v>4699044.81241</v>
+        <v>4699006.559492</v>
       </c>
       <c r="Q177" t="n">
-        <v>4923220.882307</v>
+        <v>4923172.446367</v>
       </c>
       <c r="R177" t="n">
-        <v>5064516.023088</v>
+        <v>5064454.880682</v>
       </c>
       <c r="S177" t="n">
-        <v>5152085.824164</v>
+        <v>5152008.358879</v>
       </c>
       <c r="T177" t="n">
-        <v>5205946.857076</v>
+        <v>5205847.824143</v>
       </c>
       <c r="U177" t="n">
-        <v>5238251.334945</v>
+        <v>5238122.435795</v>
       </c>
       <c r="V177" t="n">
-        <v>5253074.935129</v>
+        <v>5252901.368373</v>
       </c>
     </row>
     <row r="178">
@@ -13902,58 +13902,58 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>448.26595</v>
+        <v>448.267489</v>
       </c>
       <c r="F178" t="n">
-        <v>618.5291570000001</v>
+        <v>618.533969</v>
       </c>
       <c r="G178" t="n">
-        <v>802.154072</v>
+        <v>802.164464</v>
       </c>
       <c r="H178" t="n">
-        <v>1045.976456</v>
+        <v>1045.996227</v>
       </c>
       <c r="I178" t="n">
-        <v>1328.375497</v>
+        <v>1328.409614</v>
       </c>
       <c r="J178" t="n">
-        <v>1669.654735</v>
+        <v>1669.710628</v>
       </c>
       <c r="K178" t="n">
-        <v>2055.495803</v>
+        <v>2055.58313</v>
       </c>
       <c r="L178" t="n">
-        <v>2494.072393</v>
+        <v>2494.20456</v>
       </c>
       <c r="M178" t="n">
-        <v>3002.087132</v>
+        <v>3002.283416</v>
       </c>
       <c r="N178" t="n">
-        <v>3591.114413</v>
+        <v>3591.402293</v>
       </c>
       <c r="O178" t="n">
-        <v>4231.268475</v>
+        <v>4231.683033</v>
       </c>
       <c r="P178" t="n">
-        <v>4888.725301</v>
+        <v>4889.310429</v>
       </c>
       <c r="Q178" t="n">
-        <v>5561.628708</v>
+        <v>5562.443597</v>
       </c>
       <c r="R178" t="n">
-        <v>6265.645754</v>
+        <v>6266.776273</v>
       </c>
       <c r="S178" t="n">
-        <v>7010.473899</v>
+        <v>7012.047176</v>
       </c>
       <c r="T178" t="n">
-        <v>7787.159947</v>
+        <v>7789.367984</v>
       </c>
       <c r="U178" t="n">
-        <v>8585.097766000001</v>
+        <v>8588.247015000001</v>
       </c>
       <c r="V178" t="n">
-        <v>9424.910875</v>
+        <v>9429.551723</v>
       </c>
     </row>
     <row r="179">
@@ -13978,58 +13978,58 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>309.739897</v>
+        <v>309.740921</v>
       </c>
       <c r="F179" t="n">
-        <v>375.980373</v>
+        <v>375.983138</v>
       </c>
       <c r="G179" t="n">
-        <v>454.172005</v>
+        <v>454.177604</v>
       </c>
       <c r="H179" t="n">
-        <v>559.282798</v>
+        <v>559.292973</v>
       </c>
       <c r="I179" t="n">
-        <v>678.847805</v>
+        <v>678.864853</v>
       </c>
       <c r="J179" t="n">
-        <v>821.725941</v>
+        <v>821.753343</v>
       </c>
       <c r="K179" t="n">
-        <v>978.0608089999999</v>
+        <v>978.103024</v>
       </c>
       <c r="L179" t="n">
-        <v>1141.579741</v>
+        <v>1141.642199</v>
       </c>
       <c r="M179" t="n">
-        <v>1311.920902</v>
+        <v>1312.0104</v>
       </c>
       <c r="N179" t="n">
-        <v>1484.542343</v>
+        <v>1484.667024</v>
       </c>
       <c r="O179" t="n">
-        <v>1661.377124</v>
+        <v>1661.547702</v>
       </c>
       <c r="P179" t="n">
-        <v>1850.598257</v>
+        <v>1850.830882</v>
       </c>
       <c r="Q179" t="n">
-        <v>2072.76879</v>
+        <v>2073.090181</v>
       </c>
       <c r="R179" t="n">
-        <v>2336.420772</v>
+        <v>2336.871791</v>
       </c>
       <c r="S179" t="n">
-        <v>2641.500038</v>
+        <v>2642.141596</v>
       </c>
       <c r="T179" t="n">
-        <v>2979.56169</v>
+        <v>2980.485097</v>
       </c>
       <c r="U179" t="n">
-        <v>3348.48406</v>
+        <v>3349.837411</v>
       </c>
       <c r="V179" t="n">
-        <v>3764.821978</v>
+        <v>3766.878343</v>
       </c>
     </row>
     <row r="180">
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-5e-06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="I181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="K181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="O181" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="P181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="Q181" t="n">
         <v>-3e-06</v>
       </c>
-      <c r="F181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="G181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="H181" t="n">
+      <c r="R181" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="S181" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="T181" t="n">
         <v>1e-06</v>
       </c>
-      <c r="I181" t="n">
+      <c r="U181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="V181" t="n">
         <v>-4e-06</v>
-      </c>
-      <c r="J181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="K181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="L181" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="M181" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="R181" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="S181" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="V181" t="n">
-        <v>-3e-06</v>
       </c>
     </row>
   </sheetData>
